--- a/data/MetalliCan/pre_cleaned_data/land_table_mining.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_table_mining.xlsx
@@ -1,15 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_5EFDE0FCCC73C92FB52D4CCC6D6C3663787884B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{918E8848-1DCA-40BD-80BA-E89796738D43}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -847,8 +869,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -911,13 +933,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -955,7 +985,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -989,6 +1019,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1023,9 +1054,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1198,11 +1230,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="68.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1234,41 +1278,38 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F2" t="s">
         <v>196</v>
       </c>
       <c r="G2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H2" t="s">
-        <v>210</v>
-      </c>
-      <c r="I2" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="J2">
-        <v>1499689.86541</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>15702687.604910919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
         <v>196</v>
@@ -1277,168 +1318,183 @@
         <v>198</v>
       </c>
       <c r="H3" t="s">
-        <v>211</v>
+        <v>225</v>
+      </c>
+      <c r="I3" t="s">
+        <v>273</v>
       </c>
       <c r="J3">
-        <v>7967834.63756</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>19028718.451565798</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s">
         <v>196</v>
       </c>
       <c r="G4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H4" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="J4">
-        <v>416736.8603415595</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>26104648.817951292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J5">
+        <v>6202897.0171400001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I6" t="s">
+        <v>244</v>
+      </c>
+      <c r="J6">
+        <v>1600590.119251437</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H7" t="s">
+        <v>228</v>
+      </c>
+      <c r="J7">
+        <v>3063892.8050827952</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" t="s">
+        <v>196</v>
+      </c>
+      <c r="G8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H8" t="s">
+        <v>228</v>
+      </c>
+      <c r="J8">
+        <v>110803.86577744479</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F9" t="s">
+        <v>196</v>
+      </c>
+      <c r="G9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J9">
+        <v>21591249.4628</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C10" t="s">
         <v>101</v>
-      </c>
-      <c r="E5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" t="s">
-        <v>198</v>
-      </c>
-      <c r="H5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I5" t="s">
-        <v>242</v>
-      </c>
-      <c r="J5">
-        <v>13233210.3886</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G6" t="s">
-        <v>198</v>
-      </c>
-      <c r="H6" t="s">
-        <v>214</v>
-      </c>
-      <c r="I6" t="s">
-        <v>243</v>
-      </c>
-      <c r="J6">
-        <v>22527998.6785</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G7" t="s">
-        <v>198</v>
-      </c>
-      <c r="H7" t="s">
-        <v>211</v>
-      </c>
-      <c r="I7" t="s">
-        <v>244</v>
-      </c>
-      <c r="J7">
-        <v>11531646.5435</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" t="s">
-        <v>196</v>
-      </c>
-      <c r="G8" t="s">
-        <v>200</v>
-      </c>
-      <c r="H8" t="s">
-        <v>211</v>
-      </c>
-      <c r="I8" t="s">
-        <v>245</v>
-      </c>
-      <c r="J8">
-        <v>4950459.91493</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" t="s">
-        <v>196</v>
-      </c>
-      <c r="G9" t="s">
-        <v>198</v>
-      </c>
-      <c r="H9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J9">
-        <v>63924259.8049</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>186</v>
@@ -1453,460 +1509,475 @@
         <v>213</v>
       </c>
       <c r="I10" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J10">
-        <v>12606786.4826</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>13233210.388599999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E11" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F11" t="s">
         <v>196</v>
       </c>
       <c r="G11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H11" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="J11">
-        <v>330003.3338055482</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>1929968.1763706871</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F12" t="s">
         <v>196</v>
       </c>
       <c r="G12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H12" t="s">
-        <v>217</v>
+        <v>212</v>
+      </c>
+      <c r="I12" t="s">
+        <v>261</v>
       </c>
       <c r="J12">
-        <v>1058100.092748948</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>10276967.100669291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F13" t="s">
         <v>196</v>
       </c>
       <c r="G13" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13" t="s">
+        <v>224</v>
+      </c>
+      <c r="J13">
+        <v>9992991.5686563142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F14" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" t="s">
+        <v>199</v>
+      </c>
+      <c r="H14" t="s">
+        <v>223</v>
+      </c>
+      <c r="J14">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" t="s">
+        <v>212</v>
+      </c>
+      <c r="I15" t="s">
+        <v>261</v>
+      </c>
+      <c r="J15">
+        <v>352884.57374953461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G16" t="s">
+        <v>204</v>
+      </c>
+      <c r="H16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I16" t="s">
+        <v>251</v>
+      </c>
+      <c r="J16">
+        <v>16826817.56129609</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F17" t="s">
+        <v>196</v>
+      </c>
+      <c r="G17" t="s">
+        <v>200</v>
+      </c>
+      <c r="H17" t="s">
+        <v>212</v>
+      </c>
+      <c r="I17" t="s">
+        <v>244</v>
+      </c>
+      <c r="J17">
+        <v>1445491.9253398541</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G18" t="s">
+        <v>199</v>
+      </c>
+      <c r="H18" t="s">
+        <v>212</v>
+      </c>
+      <c r="J18">
+        <v>416736.86034155951</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F19" t="s">
+        <v>196</v>
+      </c>
+      <c r="G19" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" t="s">
+        <v>223</v>
+      </c>
+      <c r="J19">
+        <v>3714363.081590083</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H20" t="s">
+        <v>212</v>
+      </c>
+      <c r="I20" t="s">
+        <v>255</v>
+      </c>
+      <c r="J20">
+        <v>7405086.2285420913</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" t="s">
         <v>197</v>
       </c>
-      <c r="H13" t="s">
-        <v>218</v>
-      </c>
-      <c r="I13" t="s">
-        <v>247</v>
-      </c>
-      <c r="J13">
-        <v>363438.296974</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" t="s">
-        <v>187</v>
-      </c>
-      <c r="F14" t="s">
-        <v>196</v>
-      </c>
-      <c r="G14" t="s">
-        <v>201</v>
-      </c>
-      <c r="H14" t="s">
-        <v>219</v>
-      </c>
-      <c r="I14" t="s">
-        <v>248</v>
-      </c>
-      <c r="J14">
-        <v>2410689.221736038</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" t="s">
-        <v>187</v>
-      </c>
-      <c r="F15" t="s">
-        <v>196</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H21" t="s">
+        <v>226</v>
+      </c>
+      <c r="I21" t="s">
+        <v>254</v>
+      </c>
+      <c r="J21">
+        <v>1760913.595839669</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>190</v>
+      </c>
+      <c r="F22" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22" t="s">
+        <v>205</v>
+      </c>
+      <c r="H22" t="s">
+        <v>224</v>
+      </c>
+      <c r="I22" t="s">
+        <v>250</v>
+      </c>
+      <c r="J22">
+        <v>126962.74509226839</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" t="s">
+        <v>192</v>
+      </c>
+      <c r="F23" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" t="s">
+        <v>197</v>
+      </c>
+      <c r="H23" t="s">
+        <v>228</v>
+      </c>
+      <c r="J23">
+        <v>2161806.0909095029</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" t="s">
+        <v>186</v>
+      </c>
+      <c r="F24" t="s">
+        <v>196</v>
+      </c>
+      <c r="G24" t="s">
+        <v>198</v>
+      </c>
+      <c r="H24" t="s">
+        <v>214</v>
+      </c>
+      <c r="I24" t="s">
+        <v>243</v>
+      </c>
+      <c r="J24">
+        <v>22527998.6785</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" t="s">
+        <v>196</v>
+      </c>
+      <c r="G25" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" t="s">
+        <v>225</v>
+      </c>
+      <c r="I25" t="s">
+        <v>270</v>
+      </c>
+      <c r="J25">
+        <v>1341835.17078</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>192</v>
+      </c>
+      <c r="F26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" t="s">
         <v>203</v>
       </c>
-      <c r="H15" t="s">
-        <v>220</v>
-      </c>
-      <c r="J15">
-        <v>7481998.483051093</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F16" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" t="s">
-        <v>203</v>
-      </c>
-      <c r="H16" t="s">
-        <v>221</v>
-      </c>
-      <c r="I16" t="s">
-        <v>249</v>
-      </c>
-      <c r="J16">
-        <v>4789014.03756</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" t="s">
-        <v>188</v>
-      </c>
-      <c r="F17" t="s">
-        <v>196</v>
-      </c>
-      <c r="G17" t="s">
-        <v>201</v>
-      </c>
-      <c r="H17" t="s">
-        <v>222</v>
-      </c>
-      <c r="J17">
-        <v>163254.62437129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>188</v>
-      </c>
-      <c r="F18" t="s">
-        <v>196</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H26" t="s">
+        <v>212</v>
+      </c>
+      <c r="I26" t="s">
+        <v>257</v>
+      </c>
+      <c r="J26">
+        <v>3503071.0617284952</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" t="s">
         <v>198</v>
       </c>
-      <c r="H18" t="s">
-        <v>223</v>
-      </c>
-      <c r="J18">
-        <v>10572188.5661376</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" t="s">
-        <v>188</v>
-      </c>
-      <c r="F19" t="s">
-        <v>196</v>
-      </c>
-      <c r="G19" t="s">
-        <v>197</v>
-      </c>
-      <c r="H19" t="s">
-        <v>213</v>
-      </c>
-      <c r="J19">
-        <v>1510729.369309124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F20" t="s">
-        <v>196</v>
-      </c>
-      <c r="G20" t="s">
-        <v>198</v>
-      </c>
-      <c r="H20" t="s">
-        <v>223</v>
-      </c>
-      <c r="J20">
-        <v>26104648.81795129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" t="s">
-        <v>188</v>
-      </c>
-      <c r="F21" t="s">
-        <v>196</v>
-      </c>
-      <c r="G21" t="s">
-        <v>199</v>
-      </c>
-      <c r="H21" t="s">
-        <v>223</v>
-      </c>
-      <c r="J21">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" t="s">
-        <v>188</v>
-      </c>
-      <c r="F22" t="s">
-        <v>196</v>
-      </c>
-      <c r="G22" t="s">
-        <v>198</v>
-      </c>
-      <c r="H22" t="s">
-        <v>212</v>
-      </c>
-      <c r="J22">
-        <v>4354811.166996506</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" t="s">
-        <v>189</v>
-      </c>
-      <c r="F23" t="s">
-        <v>196</v>
-      </c>
-      <c r="G23" t="s">
-        <v>198</v>
-      </c>
-      <c r="H23" t="s">
-        <v>212</v>
-      </c>
-      <c r="I23" t="s">
-        <v>250</v>
-      </c>
-      <c r="J23">
-        <v>3064668.693174671</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" t="s">
-        <v>190</v>
-      </c>
-      <c r="F24" t="s">
-        <v>196</v>
-      </c>
-      <c r="G24" t="s">
-        <v>204</v>
-      </c>
-      <c r="H24" t="s">
-        <v>224</v>
-      </c>
-      <c r="J24">
-        <v>9992991.568656314</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>190</v>
-      </c>
-      <c r="F25" t="s">
-        <v>196</v>
-      </c>
-      <c r="G25" t="s">
-        <v>204</v>
-      </c>
-      <c r="H25" t="s">
-        <v>224</v>
-      </c>
-      <c r="I25" t="s">
-        <v>251</v>
-      </c>
-      <c r="J25">
-        <v>16826817.56129609</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F26" t="s">
-        <v>196</v>
-      </c>
-      <c r="G26" t="s">
-        <v>205</v>
-      </c>
-      <c r="H26" t="s">
-        <v>224</v>
-      </c>
-      <c r="I26" t="s">
-        <v>250</v>
-      </c>
-      <c r="J26">
-        <v>126962.7450922684</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" t="s">
-        <v>177</v>
-      </c>
-      <c r="E27" t="s">
-        <v>191</v>
-      </c>
-      <c r="F27" t="s">
-        <v>196</v>
-      </c>
-      <c r="G27" t="s">
-        <v>201</v>
-      </c>
       <c r="H27" t="s">
-        <v>212</v>
-      </c>
-      <c r="I27" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="J27">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>63924259.804899998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>138</v>
+      </c>
+      <c r="D28" t="s">
+        <v>180</v>
       </c>
       <c r="E28" t="s">
         <v>192</v>
@@ -1915,24 +1986,27 @@
         <v>196</v>
       </c>
       <c r="G28" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H28" t="s">
-        <v>225</v>
-      </c>
-      <c r="I28" t="s">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="J28">
-        <v>22789723.43693621</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>1141145.8646362079</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>44</v>
+      </c>
+      <c r="B29" t="s">
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>132</v>
+      </c>
+      <c r="D29" t="s">
+        <v>180</v>
       </c>
       <c r="E29" t="s">
         <v>192</v>
@@ -1941,88 +2015,76 @@
         <v>196</v>
       </c>
       <c r="G29" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29" t="s">
+        <v>212</v>
+      </c>
+      <c r="I29" t="s">
+        <v>256</v>
+      </c>
+      <c r="J29">
+        <v>15428020.65126922</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" t="s">
         <v>200</v>
       </c>
-      <c r="H29" t="s">
-        <v>225</v>
-      </c>
-      <c r="I29" t="s">
-        <v>253</v>
-      </c>
-      <c r="J29">
-        <v>5804864.894492002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" t="s">
-        <v>178</v>
-      </c>
-      <c r="E30" t="s">
-        <v>192</v>
-      </c>
-      <c r="F30" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" t="s">
-        <v>197</v>
-      </c>
       <c r="H30" t="s">
-        <v>226</v>
-      </c>
-      <c r="I30" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="J30">
-        <v>1760913.595839669</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>5293594.021862885</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F31" t="s">
         <v>196</v>
       </c>
       <c r="G31" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H31" t="s">
-        <v>227</v>
-      </c>
-      <c r="I31" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="J31">
-        <v>559241.2641449785</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>10235647.18904726</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
         <v>192</v>
@@ -2031,50 +2093,50 @@
         <v>196</v>
       </c>
       <c r="G32" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H32" t="s">
+        <v>231</v>
+      </c>
+      <c r="I32" t="s">
+        <v>264</v>
+      </c>
+      <c r="J32">
+        <v>4202253.5385999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" t="s">
+        <v>198</v>
+      </c>
+      <c r="H33" t="s">
         <v>212</v>
       </c>
-      <c r="J32">
-        <v>3512631.992361845</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E33" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" t="s">
-        <v>196</v>
-      </c>
-      <c r="G33" t="s">
-        <v>197</v>
-      </c>
-      <c r="H33" t="s">
-        <v>228</v>
+      <c r="I33" t="s">
+        <v>267</v>
       </c>
       <c r="J33">
-        <v>2161806.090909503</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>3436361.1128654238</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
         <v>192</v>
@@ -2086,59 +2148,62 @@
         <v>203</v>
       </c>
       <c r="H34" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="I34" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="J34">
-        <v>7405086.228542091</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>8409093.1265900005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="D35" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F35" t="s">
         <v>196</v>
       </c>
       <c r="G35" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H35" t="s">
-        <v>228</v>
+        <v>237</v>
+      </c>
+      <c r="I35" t="s">
+        <v>274</v>
       </c>
       <c r="J35">
-        <v>1929968.176370687</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>2331098.7137656999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E36" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F36" t="s">
         <v>196</v>
@@ -2147,76 +2212,70 @@
         <v>197</v>
       </c>
       <c r="H36" t="s">
+        <v>218</v>
+      </c>
+      <c r="I36" t="s">
+        <v>247</v>
+      </c>
+      <c r="J36">
+        <v>363438.296974</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" t="s">
+        <v>200</v>
+      </c>
+      <c r="H37" t="s">
         <v>212</v>
       </c>
-      <c r="I36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J36">
-        <v>15428020.65126922</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" t="s">
-        <v>179</v>
-      </c>
-      <c r="E37" t="s">
-        <v>192</v>
-      </c>
-      <c r="F37" t="s">
-        <v>196</v>
-      </c>
-      <c r="G37" t="s">
-        <v>197</v>
-      </c>
-      <c r="H37" t="s">
-        <v>228</v>
-      </c>
       <c r="J37">
-        <v>110803.8657774448</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>11904079.93924279</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="E38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
         <v>196</v>
       </c>
       <c r="G38" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H38" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="I38" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="J38">
-        <v>3503071.061728495</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>5574423.9812850002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
         <v>192</v>
@@ -2225,21 +2284,24 @@
         <v>196</v>
       </c>
       <c r="G39" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H39" t="s">
-        <v>229</v>
+        <v>225</v>
+      </c>
+      <c r="I39" t="s">
+        <v>253</v>
       </c>
       <c r="J39">
-        <v>989146.0724139999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>5804864.8944920022</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
         <v>192</v>
@@ -2248,79 +2310,73 @@
         <v>196</v>
       </c>
       <c r="G40" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H40" t="s">
-        <v>212</v>
-      </c>
-      <c r="I40" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="J40">
-        <v>1874190.45757726</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>240468.70558949231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>84</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>172</v>
+      </c>
+      <c r="D41" t="s">
+        <v>185</v>
       </c>
       <c r="E41" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F41" t="s">
         <v>196</v>
       </c>
       <c r="G41" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H41" t="s">
-        <v>225</v>
-      </c>
-      <c r="I41" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="J41">
-        <v>6139378.49533</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>1973892.4554655049</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E42" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F42" t="s">
         <v>196</v>
       </c>
       <c r="G42" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H42" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="J42">
-        <v>1141145.864636208</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>4412887.4395813216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E43" t="s">
         <v>192</v>
@@ -2329,99 +2385,99 @@
         <v>196</v>
       </c>
       <c r="G43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H43" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J43">
-        <v>240468.7055894923</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>989146.07241399994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>123</v>
+      </c>
+      <c r="D44" t="s">
+        <v>177</v>
       </c>
       <c r="E44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F44" t="s">
         <v>196</v>
       </c>
       <c r="G44" t="s">
+        <v>201</v>
+      </c>
+      <c r="H44" t="s">
+        <v>212</v>
+      </c>
+      <c r="I44" t="s">
+        <v>252</v>
+      </c>
+      <c r="J44">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>115</v>
+      </c>
+      <c r="E45" t="s">
+        <v>188</v>
+      </c>
+      <c r="F45" t="s">
+        <v>196</v>
+      </c>
+      <c r="G45" t="s">
+        <v>197</v>
+      </c>
+      <c r="H45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45">
+        <v>1510729.3693091241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>174</v>
+      </c>
+      <c r="E46" t="s">
+        <v>195</v>
+      </c>
+      <c r="F46" t="s">
+        <v>196</v>
+      </c>
+      <c r="G46" t="s">
         <v>203</v>
       </c>
-      <c r="H44" t="s">
-        <v>230</v>
-      </c>
-      <c r="I44" t="s">
-        <v>260</v>
-      </c>
-      <c r="J44">
-        <v>8409093.12659</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" t="s">
-        <v>192</v>
-      </c>
-      <c r="F45" t="s">
-        <v>196</v>
-      </c>
-      <c r="G45" t="s">
-        <v>198</v>
-      </c>
-      <c r="H45" t="s">
-        <v>212</v>
-      </c>
-      <c r="I45" t="s">
-        <v>261</v>
-      </c>
-      <c r="J45">
-        <v>10276967.10066929</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" t="s">
+      <c r="H46" t="s">
+        <v>213</v>
+      </c>
+      <c r="J46">
+        <v>3418676.16080696</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>54</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>142</v>
-      </c>
-      <c r="E46" t="s">
-        <v>192</v>
-      </c>
-      <c r="F46" t="s">
-        <v>196</v>
-      </c>
-      <c r="G46" t="s">
-        <v>199</v>
-      </c>
-      <c r="H46" t="s">
-        <v>212</v>
-      </c>
-      <c r="I46" t="s">
-        <v>262</v>
-      </c>
-      <c r="J46">
-        <v>948677.9026767507</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" t="s">
-        <v>143</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
@@ -2430,146 +2486,131 @@
         <v>196</v>
       </c>
       <c r="G47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H47" t="s">
         <v>212</v>
       </c>
       <c r="I47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J47">
-        <v>352884.5737495346</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>948677.90267675067</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D48" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F48" t="s">
         <v>196</v>
       </c>
       <c r="G48" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H48" t="s">
-        <v>228</v>
+        <v>223</v>
+      </c>
+      <c r="I48" t="s">
+        <v>265</v>
       </c>
       <c r="J48">
-        <v>3063892.805082795</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>24972920.132110279</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="E49" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F49" t="s">
         <v>196</v>
       </c>
       <c r="G49" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H49" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="I49" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J49">
-        <v>1039802.195699128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>3064668.6931746709</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
-      </c>
-      <c r="D50" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="E50" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F50" t="s">
         <v>196</v>
       </c>
       <c r="G50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H50" t="s">
-        <v>228</v>
+        <v>213</v>
+      </c>
+      <c r="I50" t="s">
+        <v>246</v>
       </c>
       <c r="J50">
-        <v>21591249.4628</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>12606786.4826</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" t="s">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
-      </c>
-      <c r="D51" t="s">
-        <v>181</v>
+        <v>99</v>
       </c>
       <c r="E51" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F51" t="s">
         <v>196</v>
       </c>
       <c r="G51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H51" t="s">
-        <v>212</v>
-      </c>
-      <c r="I51" t="s">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="J51">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>7967834.6375599997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E52" t="s">
         <v>192</v>
@@ -2581,30 +2622,24 @@
         <v>200</v>
       </c>
       <c r="H52" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="I52" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="J52">
-        <v>4202253.5386</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>1550354.452950391</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>149</v>
-      </c>
-      <c r="D53" t="s">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="E53" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s">
         <v>196</v>
@@ -2613,21 +2648,24 @@
         <v>197</v>
       </c>
       <c r="H53" t="s">
-        <v>232</v>
+        <v>210</v>
+      </c>
+      <c r="I53" t="s">
+        <v>241</v>
       </c>
       <c r="J53">
-        <v>1788407.819274</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>1499689.8654100001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="E54" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F54" t="s">
         <v>196</v>
@@ -2636,79 +2674,82 @@
         <v>200</v>
       </c>
       <c r="H54" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="I54" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="J54">
-        <v>1550354.452950391</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>4950459.91493</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>22</v>
+      </c>
+      <c r="B55" t="s">
+        <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>110</v>
+      </c>
+      <c r="D55" t="s">
+        <v>175</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F55" t="s">
         <v>196</v>
       </c>
       <c r="G55" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H55" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I55" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J55">
-        <v>7249147.17667</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>2410689.2217360381</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
         <v>196</v>
       </c>
       <c r="G56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H56" t="s">
-        <v>223</v>
-      </c>
-      <c r="I56" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="J56">
-        <v>24972920.13211028</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <v>1788407.8192739999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E57" t="s">
         <v>193</v>
@@ -2717,21 +2758,24 @@
         <v>196</v>
       </c>
       <c r="G57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H57" t="s">
-        <v>223</v>
+        <v>233</v>
+      </c>
+      <c r="I57" t="s">
+        <v>265</v>
       </c>
       <c r="J57">
-        <v>15702687.60491092</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>2323252.9267690452</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E58" t="s">
         <v>193</v>
@@ -2740,105 +2784,90 @@
         <v>196</v>
       </c>
       <c r="G58" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H58" t="s">
-        <v>224</v>
-      </c>
-      <c r="I58" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="J58">
-        <v>280723.3006520429</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>2689687.0630099322</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
-      </c>
-      <c r="D59" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F59" t="s">
         <v>196</v>
       </c>
       <c r="G59" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J59">
-        <v>3714363.081590083</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>163254.62437129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F60" t="s">
         <v>196</v>
       </c>
       <c r="G60" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H60" t="s">
         <v>212</v>
       </c>
-      <c r="I60" t="s">
-        <v>244</v>
-      </c>
       <c r="J60">
-        <v>1445491.925339854</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+        <v>4354811.166996506</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F61" t="s">
         <v>196</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H61" t="s">
         <v>212</v>
       </c>
-      <c r="I61" t="s">
-        <v>267</v>
-      </c>
       <c r="J61">
-        <v>3436361.112865424</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>3512631.992361845</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E62" t="s">
         <v>193</v>
@@ -2850,76 +2879,76 @@
         <v>200</v>
       </c>
       <c r="H62" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I62" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J62">
-        <v>2323252.926769045</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>2475749.7725005322</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="C63" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="E63" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F63" t="s">
         <v>196</v>
       </c>
       <c r="G63" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H63" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="I63" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="J63">
-        <v>2475749.772500532</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>22789723.436936211</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="E64" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F64" t="s">
         <v>196</v>
       </c>
       <c r="G64" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H64" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="I64" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="J64">
-        <v>6202897.01714</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>11531646.543500001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C65" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F65" t="s">
         <v>196</v>
@@ -2931,18 +2960,18 @@
         <v>225</v>
       </c>
       <c r="I65" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="J65">
-        <v>1341835.17078</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+        <v>6139378.4953300003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C66" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E66" t="s">
         <v>193</v>
@@ -2951,73 +2980,76 @@
         <v>196</v>
       </c>
       <c r="G66" t="s">
+        <v>203</v>
+      </c>
+      <c r="H66" t="s">
+        <v>224</v>
+      </c>
+      <c r="I66" t="s">
+        <v>266</v>
+      </c>
+      <c r="J66">
+        <v>280723.3006520429</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F67" t="s">
+        <v>196</v>
+      </c>
+      <c r="G67" t="s">
+        <v>198</v>
+      </c>
+      <c r="H67" t="s">
+        <v>223</v>
+      </c>
+      <c r="J67">
+        <v>10572188.566137601</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" t="s">
+        <v>168</v>
+      </c>
+      <c r="D68" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" t="s">
+        <v>194</v>
+      </c>
+      <c r="F68" t="s">
+        <v>196</v>
+      </c>
+      <c r="G68" t="s">
         <v>201</v>
       </c>
-      <c r="H66" t="s">
-        <v>225</v>
-      </c>
-      <c r="I66" t="s">
-        <v>271</v>
-      </c>
-      <c r="J66">
-        <v>1113516.59973</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" t="s">
-        <v>163</v>
-      </c>
-      <c r="E67" t="s">
-        <v>193</v>
-      </c>
-      <c r="F67" t="s">
-        <v>196</v>
-      </c>
-      <c r="G67" t="s">
-        <v>206</v>
-      </c>
-      <c r="H67" t="s">
-        <v>235</v>
-      </c>
-      <c r="J67">
-        <v>2689687.063009932</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>76</v>
-      </c>
-      <c r="C68" t="s">
-        <v>164</v>
-      </c>
-      <c r="E68" t="s">
-        <v>193</v>
-      </c>
-      <c r="F68" t="s">
-        <v>196</v>
-      </c>
-      <c r="G68" t="s">
-        <v>200</v>
-      </c>
       <c r="H68" t="s">
-        <v>236</v>
-      </c>
-      <c r="I68" t="s">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="J68">
-        <v>5574423.981285</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E69" t="s">
         <v>193</v>
@@ -3026,134 +3058,140 @@
         <v>196</v>
       </c>
       <c r="G69" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H69" t="s">
         <v>225</v>
       </c>
       <c r="I69" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J69">
-        <v>19028718.4515658</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>1113516.5997299999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
-        <v>166</v>
+        <v>107</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E70" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F70" t="s">
         <v>196</v>
       </c>
       <c r="G70" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H70" t="s">
-        <v>237</v>
-      </c>
-      <c r="I70" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
       <c r="J70">
-        <v>2331098.7137657</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>330003.3338055482</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>57</v>
+      </c>
+      <c r="B71" t="s">
+        <v>90</v>
       </c>
       <c r="C71" t="s">
-        <v>167</v>
+        <v>145</v>
+      </c>
+      <c r="D71" t="s">
+        <v>178</v>
       </c>
       <c r="E71" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F71" t="s">
         <v>196</v>
       </c>
       <c r="G71" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H71" t="s">
-        <v>212</v>
+        <v>228</v>
+      </c>
+      <c r="I71" t="s">
+        <v>254</v>
       </c>
       <c r="J71">
-        <v>11904079.93924279</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>1039802.195699128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>168</v>
-      </c>
-      <c r="D72" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F72" t="s">
         <v>196</v>
       </c>
       <c r="G72" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H72" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="J72">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>1058100.0927489479</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="C73" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F73" t="s">
         <v>196</v>
       </c>
       <c r="G73" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H73" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="J73">
-        <v>4412887.439581322</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+        <v>7481998.4830510933</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>59</v>
+      </c>
+      <c r="B74" t="s">
+        <v>93</v>
       </c>
       <c r="C74" t="s">
-        <v>170</v>
+        <v>147</v>
+      </c>
+      <c r="D74" t="s">
+        <v>181</v>
       </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F74" t="s">
         <v>196</v>
@@ -3162,82 +3200,82 @@
         <v>197</v>
       </c>
       <c r="H74" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="I74" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="J74">
-        <v>1600590.119251437</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C75" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E75" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F75" t="s">
         <v>196</v>
       </c>
       <c r="G75" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H75" t="s">
-        <v>238</v>
+        <v>227</v>
+      </c>
+      <c r="I75" t="s">
+        <v>246</v>
       </c>
       <c r="J75">
-        <v>10235647.18904726</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>559241.26414497849</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
-      </c>
-      <c r="D76" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="E76" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F76" t="s">
         <v>196</v>
       </c>
       <c r="G76" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H76" t="s">
-        <v>238</v>
+        <v>221</v>
+      </c>
+      <c r="I76" t="s">
+        <v>249</v>
       </c>
       <c r="J76">
-        <v>1973892.455465505</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>4789014.0375600001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="E77" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F77" t="s">
         <v>196</v>
@@ -3246,36 +3284,42 @@
         <v>200</v>
       </c>
       <c r="H77" t="s">
-        <v>239</v>
+        <v>225</v>
+      </c>
+      <c r="I77" t="s">
+        <v>246</v>
       </c>
       <c r="J77">
-        <v>5293594.021862885</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+        <v>7249147.17667</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="E78" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F78" t="s">
         <v>196</v>
       </c>
       <c r="G78" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H78" t="s">
-        <v>213</v>
+        <v>212</v>
+      </c>
+      <c r="I78" t="s">
+        <v>258</v>
       </c>
       <c r="J78">
-        <v>3418676.16080696</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+        <v>1874190.45757726</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>89</v>
       </c>
@@ -3295,10 +3339,10 @@
         <v>252</v>
       </c>
       <c r="J79">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>92</v>
       </c>
@@ -3318,10 +3362,10 @@
         <v>256</v>
       </c>
       <c r="J80">
-        <v>16569166.51590542</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10">
+        <v>16569166.515905419</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>94</v>
       </c>
@@ -3341,10 +3385,10 @@
         <v>265</v>
       </c>
       <c r="J81">
-        <v>28687283.21370036</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10">
+        <v>28687283.213700362</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>93</v>
       </c>
@@ -3364,10 +3408,10 @@
         <v>263</v>
       </c>
       <c r="J82">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>96</v>
       </c>
@@ -3384,10 +3428,10 @@
         <v>212</v>
       </c>
       <c r="J83">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>97</v>
       </c>
@@ -3404,10 +3448,10 @@
         <v>238</v>
       </c>
       <c r="J84">
-        <v>12209539.64451277</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10">
+        <v>12209539.644512771</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>95</v>
       </c>
@@ -3427,10 +3471,10 @@
         <v>274</v>
       </c>
       <c r="J85">
-        <v>2331098.7137657</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10">
+        <v>2331098.7137656999</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>88</v>
       </c>
@@ -3447,10 +3491,10 @@
         <v>223</v>
       </c>
       <c r="J86">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>87</v>
       </c>
@@ -3470,10 +3514,10 @@
         <v>275</v>
       </c>
       <c r="J87">
-        <v>3104130.852515586</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10">
+        <v>3104130.8525155862</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>91</v>
       </c>
@@ -3493,10 +3537,10 @@
         <v>246</v>
       </c>
       <c r="J88">
-        <v>29416961.66508541</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10">
+        <v>29416961.665085409</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>90</v>
       </c>
@@ -3516,10 +3560,15 @@
         <v>254</v>
       </c>
       <c r="J89">
-        <v>4589123.610812797</v>
+        <v>4589123.6108127972</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J89">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/land_table_mining.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_table_mining.xlsx
@@ -1,37 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_5EFDE0FCCC73C92FB52D4CCC6D6C3663787884B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{918E8848-1DCA-40BD-80BA-E89796738D43}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -869,8 +847,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -933,21 +911,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -985,7 +955,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1019,7 +989,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1054,10 +1023,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1230,23 +1198,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="68.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1278,38 +1234,41 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F2" t="s">
         <v>196</v>
       </c>
       <c r="G2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H2" t="s">
-        <v>223</v>
+        <v>210</v>
+      </c>
+      <c r="I2" t="s">
+        <v>241</v>
       </c>
       <c r="J2">
-        <v>15702687.604910919</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1499689.86541</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F3" t="s">
         <v>196</v>
@@ -1318,183 +1277,168 @@
         <v>198</v>
       </c>
       <c r="H3" t="s">
-        <v>225</v>
-      </c>
-      <c r="I3" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="J3">
-        <v>19028718.451565798</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7967834.63756</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F4" t="s">
         <v>196</v>
       </c>
       <c r="G4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J4">
+        <v>416736.8603415595</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" t="s">
         <v>198</v>
       </c>
-      <c r="H4" t="s">
-        <v>223</v>
-      </c>
-      <c r="J4">
-        <v>26104648.817951292</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F5" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" t="s">
-        <v>203</v>
-      </c>
       <c r="H5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="I5" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="J5">
-        <v>6202897.0171400001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>13233210.3886</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
         <v>196</v>
       </c>
       <c r="G6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H6" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="I6" t="s">
+        <v>243</v>
+      </c>
+      <c r="J6">
+        <v>22527998.6785</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" t="s">
+        <v>198</v>
+      </c>
+      <c r="H7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I7" t="s">
         <v>244</v>
       </c>
-      <c r="J6">
-        <v>1600590.119251437</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" t="s">
-        <v>192</v>
-      </c>
-      <c r="F7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H7" t="s">
-        <v>228</v>
-      </c>
       <c r="J7">
-        <v>3063892.8050827952</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>11531646.5435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F8" t="s">
         <v>196</v>
       </c>
       <c r="G8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H8" t="s">
-        <v>228</v>
+        <v>211</v>
+      </c>
+      <c r="I8" t="s">
+        <v>245</v>
       </c>
       <c r="J8">
-        <v>110803.86577744479</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>4950459.91493</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
-      </c>
-      <c r="D9" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F9" t="s">
         <v>196</v>
       </c>
       <c r="G9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H9" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="J9">
-        <v>21591249.4628</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>63924259.8049</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>186</v>
@@ -1509,475 +1453,460 @@
         <v>213</v>
       </c>
       <c r="I10" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J10">
-        <v>13233210.388599999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+        <v>12606786.4826</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F11" t="s">
         <v>196</v>
       </c>
       <c r="G11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" t="s">
+        <v>216</v>
+      </c>
+      <c r="J11">
+        <v>330003.3338055482</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>187</v>
+      </c>
+      <c r="F12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G12" t="s">
+        <v>202</v>
+      </c>
+      <c r="H12" t="s">
+        <v>217</v>
+      </c>
+      <c r="J12">
+        <v>1058100.092748948</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F13" t="s">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
         <v>197</v>
       </c>
-      <c r="H11" t="s">
-        <v>228</v>
-      </c>
-      <c r="J11">
-        <v>1929968.1763706871</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" t="s">
-        <v>192</v>
-      </c>
-      <c r="F12" t="s">
-        <v>196</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H13" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" t="s">
+        <v>247</v>
+      </c>
+      <c r="J13">
+        <v>363438.296974</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" t="s">
+        <v>219</v>
+      </c>
+      <c r="I14" t="s">
+        <v>248</v>
+      </c>
+      <c r="J14">
+        <v>2410689.221736038</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G15" t="s">
+        <v>203</v>
+      </c>
+      <c r="H15" t="s">
+        <v>220</v>
+      </c>
+      <c r="J15">
+        <v>7481998.483051093</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G16" t="s">
+        <v>203</v>
+      </c>
+      <c r="H16" t="s">
+        <v>221</v>
+      </c>
+      <c r="I16" t="s">
+        <v>249</v>
+      </c>
+      <c r="J16">
+        <v>4789014.03756</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>188</v>
+      </c>
+      <c r="F17" t="s">
+        <v>196</v>
+      </c>
+      <c r="G17" t="s">
+        <v>201</v>
+      </c>
+      <c r="H17" t="s">
+        <v>222</v>
+      </c>
+      <c r="J17">
+        <v>163254.62437129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G18" t="s">
         <v>198</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H18" t="s">
+        <v>223</v>
+      </c>
+      <c r="J18">
+        <v>10572188.5661376</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" t="s">
+        <v>188</v>
+      </c>
+      <c r="F19" t="s">
+        <v>196</v>
+      </c>
+      <c r="G19" t="s">
+        <v>197</v>
+      </c>
+      <c r="H19" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19">
+        <v>1510729.369309124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F20" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H20" t="s">
+        <v>223</v>
+      </c>
+      <c r="J20">
+        <v>26104648.81795129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E21" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" t="s">
+        <v>199</v>
+      </c>
+      <c r="H21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J21">
+        <v>10340795.84070311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" t="s">
+        <v>188</v>
+      </c>
+      <c r="F22" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22" t="s">
+        <v>198</v>
+      </c>
+      <c r="H22" t="s">
         <v>212</v>
       </c>
-      <c r="I12" t="s">
-        <v>261</v>
-      </c>
-      <c r="J12">
-        <v>10276967.100669291</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="J22">
+        <v>4354811.166996506</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
+        <v>189</v>
+      </c>
+      <c r="F23" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" t="s">
+        <v>198</v>
+      </c>
+      <c r="H23" t="s">
+        <v>212</v>
+      </c>
+      <c r="I23" t="s">
+        <v>250</v>
+      </c>
+      <c r="J23">
+        <v>3064668.693174671</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C24" t="s">
         <v>120</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E24" t="s">
         <v>190</v>
       </c>
-      <c r="F13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="F24" t="s">
+        <v>196</v>
+      </c>
+      <c r="G24" t="s">
         <v>204</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H24" t="s">
         <v>224</v>
       </c>
-      <c r="J13">
-        <v>9992991.5686563142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" t="s">
-        <v>176</v>
-      </c>
-      <c r="E14" t="s">
-        <v>188</v>
-      </c>
-      <c r="F14" t="s">
-        <v>196</v>
-      </c>
-      <c r="G14" t="s">
-        <v>199</v>
-      </c>
-      <c r="H14" t="s">
-        <v>223</v>
-      </c>
-      <c r="J14">
-        <v>10340795.840703109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" t="s">
-        <v>192</v>
-      </c>
-      <c r="F15" t="s">
-        <v>196</v>
-      </c>
-      <c r="G15" t="s">
-        <v>200</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="J24">
+        <v>9992991.568656314</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" t="s">
+        <v>196</v>
+      </c>
+      <c r="G25" t="s">
+        <v>204</v>
+      </c>
+      <c r="H25" t="s">
+        <v>224</v>
+      </c>
+      <c r="I25" t="s">
+        <v>251</v>
+      </c>
+      <c r="J25">
+        <v>16826817.56129609</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" t="s">
+        <v>205</v>
+      </c>
+      <c r="H26" t="s">
+        <v>224</v>
+      </c>
+      <c r="I26" t="s">
+        <v>250</v>
+      </c>
+      <c r="J26">
+        <v>126962.7450922684</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" t="s">
+        <v>191</v>
+      </c>
+      <c r="F27" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" t="s">
+        <v>201</v>
+      </c>
+      <c r="H27" t="s">
         <v>212</v>
       </c>
-      <c r="I15" t="s">
-        <v>261</v>
-      </c>
-      <c r="J15">
-        <v>352884.57374953461</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16" t="s">
-        <v>190</v>
-      </c>
-      <c r="F16" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" t="s">
-        <v>204</v>
-      </c>
-      <c r="H16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I16" t="s">
-        <v>251</v>
-      </c>
-      <c r="J16">
-        <v>16826817.56129609</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E17" t="s">
-        <v>193</v>
-      </c>
-      <c r="F17" t="s">
-        <v>196</v>
-      </c>
-      <c r="G17" t="s">
-        <v>200</v>
-      </c>
-      <c r="H17" t="s">
-        <v>212</v>
-      </c>
-      <c r="I17" t="s">
-        <v>244</v>
-      </c>
-      <c r="J17">
-        <v>1445491.9253398541</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" t="s">
-        <v>186</v>
-      </c>
-      <c r="F18" t="s">
-        <v>196</v>
-      </c>
-      <c r="G18" t="s">
-        <v>199</v>
-      </c>
-      <c r="H18" t="s">
-        <v>212</v>
-      </c>
-      <c r="J18">
-        <v>416736.86034155951</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>155</v>
-      </c>
-      <c r="D19" t="s">
-        <v>182</v>
-      </c>
-      <c r="E19" t="s">
-        <v>193</v>
-      </c>
-      <c r="F19" t="s">
-        <v>196</v>
-      </c>
-      <c r="G19" t="s">
-        <v>199</v>
-      </c>
-      <c r="H19" t="s">
-        <v>223</v>
-      </c>
-      <c r="J19">
-        <v>3714363.081590083</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" t="s">
-        <v>192</v>
-      </c>
-      <c r="F20" t="s">
-        <v>196</v>
-      </c>
-      <c r="G20" t="s">
-        <v>203</v>
-      </c>
-      <c r="H20" t="s">
-        <v>212</v>
-      </c>
-      <c r="I20" t="s">
-        <v>255</v>
-      </c>
-      <c r="J20">
-        <v>7405086.2285420913</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" t="s">
-        <v>178</v>
-      </c>
-      <c r="E21" t="s">
-        <v>192</v>
-      </c>
-      <c r="F21" t="s">
-        <v>196</v>
-      </c>
-      <c r="G21" t="s">
-        <v>197</v>
-      </c>
-      <c r="H21" t="s">
-        <v>226</v>
-      </c>
-      <c r="I21" t="s">
-        <v>254</v>
-      </c>
-      <c r="J21">
-        <v>1760913.595839669</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" t="s">
-        <v>190</v>
-      </c>
-      <c r="F22" t="s">
-        <v>196</v>
-      </c>
-      <c r="G22" t="s">
-        <v>205</v>
-      </c>
-      <c r="H22" t="s">
-        <v>224</v>
-      </c>
-      <c r="I22" t="s">
-        <v>250</v>
-      </c>
-      <c r="J22">
-        <v>126962.74509226839</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>129</v>
-      </c>
-      <c r="D23" t="s">
-        <v>179</v>
-      </c>
-      <c r="E23" t="s">
-        <v>192</v>
-      </c>
-      <c r="F23" t="s">
-        <v>196</v>
-      </c>
-      <c r="G23" t="s">
-        <v>197</v>
-      </c>
-      <c r="H23" t="s">
-        <v>228</v>
-      </c>
-      <c r="J23">
-        <v>2161806.0909095029</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" t="s">
-        <v>186</v>
-      </c>
-      <c r="F24" t="s">
-        <v>196</v>
-      </c>
-      <c r="G24" t="s">
-        <v>198</v>
-      </c>
-      <c r="H24" t="s">
-        <v>214</v>
-      </c>
-      <c r="I24" t="s">
-        <v>243</v>
-      </c>
-      <c r="J24">
-        <v>22527998.6785</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>161</v>
-      </c>
-      <c r="E25" t="s">
-        <v>193</v>
-      </c>
-      <c r="F25" t="s">
-        <v>196</v>
-      </c>
-      <c r="G25" t="s">
-        <v>200</v>
-      </c>
-      <c r="H25" t="s">
-        <v>225</v>
-      </c>
-      <c r="I25" t="s">
-        <v>270</v>
-      </c>
-      <c r="J25">
-        <v>1341835.17078</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>192</v>
-      </c>
-      <c r="F26" t="s">
-        <v>196</v>
-      </c>
-      <c r="G26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H26" t="s">
-        <v>212</v>
-      </c>
-      <c r="I26" t="s">
-        <v>257</v>
-      </c>
-      <c r="J26">
-        <v>3503071.0617284952</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" t="s">
-        <v>186</v>
-      </c>
-      <c r="F27" t="s">
-        <v>196</v>
-      </c>
-      <c r="G27" t="s">
-        <v>198</v>
-      </c>
-      <c r="H27" t="s">
-        <v>215</v>
+      <c r="I27" t="s">
+        <v>252</v>
       </c>
       <c r="J27">
-        <v>63924259.804899998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7644288.851632554</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" t="s">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
         <v>192</v>
@@ -1986,27 +1915,24 @@
         <v>196</v>
       </c>
       <c r="G28" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H28" t="s">
-        <v>212</v>
+        <v>225</v>
+      </c>
+      <c r="I28" t="s">
+        <v>250</v>
       </c>
       <c r="J28">
-        <v>1141145.8646362079</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+        <v>22789723.43693621</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" t="s">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s">
         <v>192</v>
@@ -2015,76 +1941,88 @@
         <v>196</v>
       </c>
       <c r="G29" t="s">
+        <v>200</v>
+      </c>
+      <c r="H29" t="s">
+        <v>225</v>
+      </c>
+      <c r="I29" t="s">
+        <v>253</v>
+      </c>
+      <c r="J29">
+        <v>5804864.894492002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F30" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" t="s">
         <v>197</v>
       </c>
-      <c r="H29" t="s">
-        <v>212</v>
-      </c>
-      <c r="I29" t="s">
-        <v>256</v>
-      </c>
-      <c r="J29">
-        <v>15428020.65126922</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" t="s">
-        <v>195</v>
-      </c>
-      <c r="F30" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" t="s">
-        <v>200</v>
-      </c>
       <c r="H30" t="s">
-        <v>239</v>
+        <v>226</v>
+      </c>
+      <c r="I30" t="s">
+        <v>254</v>
       </c>
       <c r="J30">
-        <v>5293594.021862885</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1760913.595839669</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E31" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F31" t="s">
         <v>196</v>
       </c>
       <c r="G31" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H31" t="s">
-        <v>238</v>
+        <v>227</v>
+      </c>
+      <c r="I31" t="s">
+        <v>246</v>
       </c>
       <c r="J31">
-        <v>10235647.18904726</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+        <v>559241.2641449785</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
         <v>192</v>
@@ -2093,50 +2031,50 @@
         <v>196</v>
       </c>
       <c r="G32" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H32" t="s">
-        <v>231</v>
-      </c>
-      <c r="I32" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="J32">
-        <v>4202253.5385999996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3512631.992361845</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>157</v>
+        <v>129</v>
+      </c>
+      <c r="D33" t="s">
+        <v>179</v>
       </c>
       <c r="E33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F33" t="s">
         <v>196</v>
       </c>
       <c r="G33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H33" t="s">
-        <v>212</v>
-      </c>
-      <c r="I33" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="J33">
-        <v>3436361.1128654238</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2161806.090909503</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E34" t="s">
         <v>192</v>
@@ -2148,62 +2086,59 @@
         <v>203</v>
       </c>
       <c r="H34" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="I34" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J34">
-        <v>8409093.1265900005</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7405086.228542091</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F35" t="s">
         <v>196</v>
       </c>
       <c r="G35" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H35" t="s">
-        <v>237</v>
-      </c>
-      <c r="I35" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="J35">
-        <v>2331098.7137656999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1929968.176370687</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F36" t="s">
         <v>196</v>
@@ -2212,70 +2147,76 @@
         <v>197</v>
       </c>
       <c r="H36" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I36" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="J36">
-        <v>363438.296974</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+        <v>15428020.65126922</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>133</v>
+      </c>
+      <c r="D37" t="s">
+        <v>179</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F37" t="s">
         <v>196</v>
       </c>
       <c r="G37" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H37" t="s">
+        <v>228</v>
+      </c>
+      <c r="J37">
+        <v>110803.8657774448</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" t="s">
+        <v>196</v>
+      </c>
+      <c r="G38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H38" t="s">
         <v>212</v>
       </c>
-      <c r="J37">
-        <v>11904079.93924279</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" t="s">
-        <v>164</v>
-      </c>
-      <c r="E38" t="s">
-        <v>193</v>
-      </c>
-      <c r="F38" t="s">
-        <v>196</v>
-      </c>
-      <c r="G38" t="s">
-        <v>200</v>
-      </c>
-      <c r="H38" t="s">
-        <v>236</v>
-      </c>
       <c r="I38" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="J38">
-        <v>5574423.9812850002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3503071.061728495</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
         <v>192</v>
@@ -2284,24 +2225,21 @@
         <v>196</v>
       </c>
       <c r="G39" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H39" t="s">
-        <v>225</v>
-      </c>
-      <c r="I39" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="J39">
-        <v>5804864.8944920022</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+        <v>989146.0724139999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
         <v>192</v>
@@ -2310,73 +2248,79 @@
         <v>196</v>
       </c>
       <c r="G40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H40" t="s">
+        <v>212</v>
+      </c>
+      <c r="I40" t="s">
+        <v>258</v>
+      </c>
+      <c r="J40">
+        <v>1874190.45757726</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>192</v>
+      </c>
+      <c r="F41" t="s">
+        <v>196</v>
+      </c>
+      <c r="G41" t="s">
+        <v>200</v>
+      </c>
+      <c r="H41" t="s">
         <v>225</v>
       </c>
-      <c r="J40">
-        <v>240468.70558949231</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>84</v>
-      </c>
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" t="s">
-        <v>172</v>
-      </c>
-      <c r="D41" t="s">
-        <v>185</v>
-      </c>
-      <c r="E41" t="s">
-        <v>194</v>
-      </c>
-      <c r="F41" t="s">
-        <v>196</v>
-      </c>
-      <c r="G41" t="s">
-        <v>197</v>
-      </c>
-      <c r="H41" t="s">
-        <v>238</v>
+      <c r="I41" t="s">
+        <v>259</v>
       </c>
       <c r="J41">
-        <v>1973892.4554655049</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+        <v>6139378.49533</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>169</v>
+        <v>138</v>
+      </c>
+      <c r="D42" t="s">
+        <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F42" t="s">
         <v>196</v>
       </c>
       <c r="G42" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H42" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="J42">
-        <v>4412887.4395813216</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1141145.864636208</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E43" t="s">
         <v>192</v>
@@ -2385,99 +2329,99 @@
         <v>196</v>
       </c>
       <c r="G43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H43" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J43">
-        <v>989146.07241399994</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+        <v>240468.7055894923</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D44" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="E44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F44" t="s">
         <v>196</v>
       </c>
       <c r="G44" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H44" t="s">
+        <v>230</v>
+      </c>
+      <c r="I44" t="s">
+        <v>260</v>
+      </c>
+      <c r="J44">
+        <v>8409093.12659</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" t="s">
+        <v>196</v>
+      </c>
+      <c r="G45" t="s">
+        <v>198</v>
+      </c>
+      <c r="H45" t="s">
         <v>212</v>
       </c>
-      <c r="I44" t="s">
-        <v>252</v>
-      </c>
-      <c r="J44">
-        <v>7644288.8516325541</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" t="s">
-        <v>115</v>
-      </c>
-      <c r="E45" t="s">
-        <v>188</v>
-      </c>
-      <c r="F45" t="s">
-        <v>196</v>
-      </c>
-      <c r="G45" t="s">
-        <v>197</v>
-      </c>
-      <c r="H45" t="s">
-        <v>213</v>
+      <c r="I45" t="s">
+        <v>261</v>
       </c>
       <c r="J45">
-        <v>1510729.3693091241</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+        <v>10276967.10066929</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F46" t="s">
         <v>196</v>
       </c>
       <c r="G46" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H46" t="s">
-        <v>213</v>
+        <v>212</v>
+      </c>
+      <c r="I46" t="s">
+        <v>262</v>
       </c>
       <c r="J46">
-        <v>3418676.16080696</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+        <v>948677.9026767507</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
@@ -2486,131 +2430,146 @@
         <v>196</v>
       </c>
       <c r="G47" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H47" t="s">
         <v>212</v>
       </c>
       <c r="I47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J47">
-        <v>948677.90267675067</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+        <v>352884.5737495346</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D48" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E48" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F48" t="s">
         <v>196</v>
       </c>
       <c r="G48" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H48" t="s">
-        <v>223</v>
-      </c>
-      <c r="I48" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="J48">
-        <v>24972920.132110279</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3063892.805082795</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>57</v>
+      </c>
+      <c r="B49" t="s">
+        <v>90</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>145</v>
+      </c>
+      <c r="D49" t="s">
+        <v>178</v>
       </c>
       <c r="E49" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F49" t="s">
         <v>196</v>
       </c>
       <c r="G49" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H49" t="s">
+        <v>228</v>
+      </c>
+      <c r="I49" t="s">
+        <v>254</v>
+      </c>
+      <c r="J49">
+        <v>1039802.195699128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" t="s">
+        <v>179</v>
+      </c>
+      <c r="E50" t="s">
+        <v>192</v>
+      </c>
+      <c r="F50" t="s">
+        <v>196</v>
+      </c>
+      <c r="G50" t="s">
+        <v>197</v>
+      </c>
+      <c r="H50" t="s">
+        <v>228</v>
+      </c>
+      <c r="J50">
+        <v>21591249.4628</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" t="s">
+        <v>181</v>
+      </c>
+      <c r="E51" t="s">
+        <v>192</v>
+      </c>
+      <c r="F51" t="s">
+        <v>196</v>
+      </c>
+      <c r="G51" t="s">
+        <v>197</v>
+      </c>
+      <c r="H51" t="s">
         <v>212</v>
       </c>
-      <c r="I49" t="s">
-        <v>250</v>
-      </c>
-      <c r="J49">
-        <v>3064668.6931746709</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E50" t="s">
-        <v>186</v>
-      </c>
-      <c r="F50" t="s">
-        <v>196</v>
-      </c>
-      <c r="G50" t="s">
-        <v>198</v>
-      </c>
-      <c r="H50" t="s">
-        <v>213</v>
-      </c>
-      <c r="I50" t="s">
-        <v>246</v>
-      </c>
-      <c r="J50">
-        <v>12606786.4826</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" t="s">
-        <v>99</v>
-      </c>
-      <c r="E51" t="s">
-        <v>186</v>
-      </c>
-      <c r="F51" t="s">
-        <v>196</v>
-      </c>
-      <c r="G51" t="s">
-        <v>198</v>
-      </c>
-      <c r="H51" t="s">
-        <v>211</v>
+      <c r="I51" t="s">
+        <v>263</v>
       </c>
       <c r="J51">
-        <v>7967834.6375599997</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1464485.501369824</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E52" t="s">
         <v>192</v>
@@ -2622,24 +2581,30 @@
         <v>200</v>
       </c>
       <c r="H52" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I52" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="J52">
-        <v>1550354.452950391</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+        <v>4202253.5386</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>90</v>
       </c>
       <c r="C53" t="s">
-        <v>98</v>
+        <v>149</v>
+      </c>
+      <c r="D53" t="s">
+        <v>178</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F53" t="s">
         <v>196</v>
@@ -2648,24 +2613,21 @@
         <v>197</v>
       </c>
       <c r="H53" t="s">
-        <v>210</v>
-      </c>
-      <c r="I53" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="J53">
-        <v>1499689.8654100001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1788407.819274</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="E54" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F54" t="s">
         <v>196</v>
@@ -2674,82 +2636,79 @@
         <v>200</v>
       </c>
       <c r="H54" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="I54" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="J54">
-        <v>4950459.91493</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1550354.452950391</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>22</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
-      </c>
-      <c r="D55" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="E55" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F55" t="s">
         <v>196</v>
       </c>
       <c r="G55" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H55" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="I55" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J55">
-        <v>2410689.2217360381</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7249147.17667</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D56" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F56" t="s">
         <v>196</v>
       </c>
       <c r="G56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H56" t="s">
-        <v>232</v>
+        <v>223</v>
+      </c>
+      <c r="I56" t="s">
+        <v>265</v>
       </c>
       <c r="J56">
-        <v>1788407.8192739999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+        <v>24972920.13211028</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E57" t="s">
         <v>193</v>
@@ -2758,24 +2717,21 @@
         <v>196</v>
       </c>
       <c r="G57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H57" t="s">
-        <v>233</v>
-      </c>
-      <c r="I57" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="J57">
-        <v>2323252.9267690452</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+        <v>15702687.60491092</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E58" t="s">
         <v>193</v>
@@ -2784,90 +2740,105 @@
         <v>196</v>
       </c>
       <c r="G58" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H58" t="s">
-        <v>235</v>
+        <v>224</v>
+      </c>
+      <c r="I58" t="s">
+        <v>266</v>
       </c>
       <c r="J58">
-        <v>2689687.0630099322</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+        <v>280723.3006520429</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>67</v>
+      </c>
+      <c r="B59" t="s">
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>113</v>
+        <v>155</v>
+      </c>
+      <c r="D59" t="s">
+        <v>182</v>
       </c>
       <c r="E59" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F59" t="s">
         <v>196</v>
       </c>
       <c r="G59" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J59">
-        <v>163254.62437129</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3714363.081590083</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="E60" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F60" t="s">
         <v>196</v>
       </c>
       <c r="G60" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H60" t="s">
         <v>212</v>
       </c>
+      <c r="I60" t="s">
+        <v>244</v>
+      </c>
       <c r="J60">
-        <v>4354811.166996506</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1445491.925339854</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="E61" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F61" t="s">
         <v>196</v>
       </c>
       <c r="G61" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H61" t="s">
         <v>212</v>
       </c>
+      <c r="I61" t="s">
+        <v>267</v>
+      </c>
       <c r="J61">
-        <v>3512631.992361845</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3436361.112865424</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E62" t="s">
         <v>193</v>
@@ -2879,76 +2850,76 @@
         <v>200</v>
       </c>
       <c r="H62" t="s">
+        <v>233</v>
+      </c>
+      <c r="I62" t="s">
+        <v>265</v>
+      </c>
+      <c r="J62">
+        <v>2323252.926769045</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" t="s">
+        <v>193</v>
+      </c>
+      <c r="F63" t="s">
+        <v>196</v>
+      </c>
+      <c r="G63" t="s">
+        <v>200</v>
+      </c>
+      <c r="H63" t="s">
         <v>234</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I63" t="s">
         <v>268</v>
       </c>
-      <c r="J62">
-        <v>2475749.7725005322</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>36</v>
-      </c>
-      <c r="C63" t="s">
-        <v>124</v>
-      </c>
-      <c r="E63" t="s">
-        <v>192</v>
-      </c>
-      <c r="F63" t="s">
-        <v>196</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="J63">
+        <v>2475749.772500532</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" t="s">
+        <v>160</v>
+      </c>
+      <c r="E64" t="s">
+        <v>193</v>
+      </c>
+      <c r="F64" t="s">
+        <v>196</v>
+      </c>
+      <c r="G64" t="s">
         <v>203</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H64" t="s">
         <v>225</v>
       </c>
-      <c r="I63" t="s">
-        <v>250</v>
-      </c>
-      <c r="J63">
-        <v>22789723.436936211</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="C64" t="s">
-        <v>103</v>
-      </c>
-      <c r="E64" t="s">
-        <v>186</v>
-      </c>
-      <c r="F64" t="s">
-        <v>196</v>
-      </c>
-      <c r="G64" t="s">
-        <v>198</v>
-      </c>
-      <c r="H64" t="s">
-        <v>211</v>
-      </c>
       <c r="I64" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="J64">
-        <v>11531646.543500001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+        <v>6202897.01714</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E65" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F65" t="s">
         <v>196</v>
@@ -2960,18 +2931,18 @@
         <v>225</v>
       </c>
       <c r="I65" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="J65">
-        <v>6139378.4953300003</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1341835.17078</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E66" t="s">
         <v>193</v>
@@ -2980,76 +2951,73 @@
         <v>196</v>
       </c>
       <c r="G66" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I66" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J66">
-        <v>280723.3006520429</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1113516.59973</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="E67" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F67" t="s">
         <v>196</v>
       </c>
       <c r="G67" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="H67" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="J67">
-        <v>10572188.566137601</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2689687.063009932</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>168</v>
-      </c>
-      <c r="D68" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="E68" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F68" t="s">
         <v>196</v>
       </c>
       <c r="G68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H68" t="s">
-        <v>212</v>
+        <v>236</v>
+      </c>
+      <c r="I68" t="s">
+        <v>272</v>
       </c>
       <c r="J68">
-        <v>517003.99124031531</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+        <v>5574423.981285</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E69" t="s">
         <v>193</v>
@@ -3058,140 +3026,134 @@
         <v>196</v>
       </c>
       <c r="G69" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H69" t="s">
         <v>225</v>
       </c>
       <c r="I69" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J69">
-        <v>1113516.5997299999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19028718.4515658</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="D70" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E70" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F70" t="s">
         <v>196</v>
       </c>
       <c r="G70" t="s">
+        <v>199</v>
+      </c>
+      <c r="H70" t="s">
+        <v>237</v>
+      </c>
+      <c r="I70" t="s">
+        <v>274</v>
+      </c>
+      <c r="J70">
+        <v>2331098.7137657</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" t="s">
+        <v>167</v>
+      </c>
+      <c r="E71" t="s">
+        <v>193</v>
+      </c>
+      <c r="F71" t="s">
+        <v>196</v>
+      </c>
+      <c r="G71" t="s">
+        <v>200</v>
+      </c>
+      <c r="H71" t="s">
+        <v>212</v>
+      </c>
+      <c r="J71">
+        <v>11904079.93924279</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" t="s">
+        <v>96</v>
+      </c>
+      <c r="C72" t="s">
+        <v>168</v>
+      </c>
+      <c r="D72" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" t="s">
+        <v>194</v>
+      </c>
+      <c r="F72" t="s">
+        <v>196</v>
+      </c>
+      <c r="G72" t="s">
         <v>201</v>
       </c>
-      <c r="H70" t="s">
-        <v>216</v>
-      </c>
-      <c r="J70">
-        <v>330003.3338055482</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>57</v>
-      </c>
-      <c r="B71" t="s">
-        <v>90</v>
-      </c>
-      <c r="C71" t="s">
-        <v>145</v>
-      </c>
-      <c r="D71" t="s">
-        <v>178</v>
-      </c>
-      <c r="E71" t="s">
-        <v>192</v>
-      </c>
-      <c r="F71" t="s">
-        <v>196</v>
-      </c>
-      <c r="G71" t="s">
+      <c r="H72" t="s">
+        <v>212</v>
+      </c>
+      <c r="J72">
+        <v>517003.9912403153</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" t="s">
+        <v>194</v>
+      </c>
+      <c r="F73" t="s">
+        <v>196</v>
+      </c>
+      <c r="G73" t="s">
         <v>201</v>
       </c>
-      <c r="H71" t="s">
-        <v>228</v>
-      </c>
-      <c r="I71" t="s">
-        <v>254</v>
-      </c>
-      <c r="J71">
-        <v>1039802.195699128</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" t="s">
-        <v>108</v>
-      </c>
-      <c r="E72" t="s">
-        <v>187</v>
-      </c>
-      <c r="F72" t="s">
-        <v>196</v>
-      </c>
-      <c r="G72" t="s">
-        <v>202</v>
-      </c>
-      <c r="H72" t="s">
-        <v>217</v>
-      </c>
-      <c r="J72">
-        <v>1058100.0927489479</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" t="s">
-        <v>111</v>
-      </c>
-      <c r="E73" t="s">
-        <v>187</v>
-      </c>
-      <c r="F73" t="s">
-        <v>196</v>
-      </c>
-      <c r="G73" t="s">
-        <v>203</v>
-      </c>
       <c r="H73" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="J73">
-        <v>7481998.4830510933</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+        <v>4412887.439581322</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>59</v>
-      </c>
-      <c r="B74" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C74" t="s">
-        <v>147</v>
-      </c>
-      <c r="D74" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E74" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F74" t="s">
         <v>196</v>
@@ -3200,82 +3162,82 @@
         <v>197</v>
       </c>
       <c r="H74" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="I74" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="J74">
-        <v>1464485.5013698239</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1600590.119251437</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D75" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E75" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F75" t="s">
         <v>196</v>
       </c>
       <c r="G75" t="s">
+        <v>201</v>
+      </c>
+      <c r="H75" t="s">
+        <v>238</v>
+      </c>
+      <c r="J75">
+        <v>10235647.18904726</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" t="s">
+        <v>97</v>
+      </c>
+      <c r="C76" t="s">
+        <v>172</v>
+      </c>
+      <c r="D76" t="s">
+        <v>185</v>
+      </c>
+      <c r="E76" t="s">
+        <v>194</v>
+      </c>
+      <c r="F76" t="s">
+        <v>196</v>
+      </c>
+      <c r="G76" t="s">
         <v>197</v>
       </c>
-      <c r="H75" t="s">
-        <v>227</v>
-      </c>
-      <c r="I75" t="s">
-        <v>246</v>
-      </c>
-      <c r="J75">
-        <v>559241.26414497849</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="E76" t="s">
-        <v>188</v>
-      </c>
-      <c r="F76" t="s">
-        <v>196</v>
-      </c>
-      <c r="G76" t="s">
-        <v>203</v>
-      </c>
       <c r="H76" t="s">
-        <v>221</v>
-      </c>
-      <c r="I76" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="J76">
-        <v>4789014.0375600001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1973892.455465505</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="E77" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F77" t="s">
         <v>196</v>
@@ -3284,42 +3246,36 @@
         <v>200</v>
       </c>
       <c r="H77" t="s">
-        <v>225</v>
-      </c>
-      <c r="I77" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J77">
-        <v>7249147.17667</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+        <v>5293594.021862885</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F78" t="s">
         <v>196</v>
       </c>
       <c r="G78" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H78" t="s">
-        <v>212</v>
-      </c>
-      <c r="I78" t="s">
-        <v>258</v>
+        <v>213</v>
       </c>
       <c r="J78">
-        <v>1874190.45757726</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3418676.16080696</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="B79" t="s">
         <v>89</v>
       </c>
@@ -3339,10 +3295,10 @@
         <v>252</v>
       </c>
       <c r="J79">
-        <v>7644288.8516325541</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7644288.851632554</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="B80" t="s">
         <v>92</v>
       </c>
@@ -3362,10 +3318,10 @@
         <v>256</v>
       </c>
       <c r="J80">
-        <v>16569166.515905419</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+        <v>16569166.51590542</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10">
       <c r="B81" t="s">
         <v>94</v>
       </c>
@@ -3385,10 +3341,10 @@
         <v>265</v>
       </c>
       <c r="J81">
-        <v>28687283.213700362</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+        <v>28687283.21370036</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10">
       <c r="B82" t="s">
         <v>93</v>
       </c>
@@ -3408,10 +3364,10 @@
         <v>263</v>
       </c>
       <c r="J82">
-        <v>1464485.5013698239</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+        <v>1464485.501369824</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10">
       <c r="B83" t="s">
         <v>96</v>
       </c>
@@ -3428,10 +3384,10 @@
         <v>212</v>
       </c>
       <c r="J83">
-        <v>517003.99124031531</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+        <v>517003.9912403153</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10">
       <c r="B84" t="s">
         <v>97</v>
       </c>
@@ -3448,10 +3404,10 @@
         <v>238</v>
       </c>
       <c r="J84">
-        <v>12209539.644512771</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+        <v>12209539.64451277</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10">
       <c r="B85" t="s">
         <v>95</v>
       </c>
@@ -3471,10 +3427,10 @@
         <v>274</v>
       </c>
       <c r="J85">
-        <v>2331098.7137656999</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+        <v>2331098.7137657</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10">
       <c r="B86" t="s">
         <v>88</v>
       </c>
@@ -3491,10 +3447,10 @@
         <v>223</v>
       </c>
       <c r="J86">
-        <v>10340795.840703109</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+        <v>10340795.84070311</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10">
       <c r="B87" t="s">
         <v>87</v>
       </c>
@@ -3514,10 +3470,10 @@
         <v>275</v>
       </c>
       <c r="J87">
-        <v>3104130.8525155862</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+        <v>3104130.852515586</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10">
       <c r="B88" t="s">
         <v>91</v>
       </c>
@@ -3537,10 +3493,10 @@
         <v>246</v>
       </c>
       <c r="J88">
-        <v>29416961.665085409</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+        <v>29416961.66508541</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10">
       <c r="B89" t="s">
         <v>90</v>
       </c>
@@ -3560,15 +3516,10 @@
         <v>254</v>
       </c>
       <c r="J89">
-        <v>4589123.6108127972</v>
+        <v>4589123.610812797</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J89">
-      <sortCondition ref="C1"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/land_table_mining.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_table_mining.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_5EFDE0FCCC73C92FB52D4CBDFDEB18C1787884B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D6B537E-6173-4DF7-9D76-ED067FF1988D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="276">
   <si>
     <t>main_id</t>
   </si>
@@ -847,8 +856,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -911,13 +920,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -955,7 +972,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -989,6 +1006,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1023,9 +1041,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1198,11 +1217,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K89"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="68.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1225,50 +1257,53 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F2" t="s">
         <v>196</v>
       </c>
       <c r="G2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H2" t="s">
-        <v>210</v>
+        <v>199</v>
+      </c>
+      <c r="H2">
+        <v>15702687.604910901</v>
       </c>
       <c r="I2" t="s">
-        <v>241</v>
-      </c>
-      <c r="J2">
-        <v>1499689.86541</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>223</v>
+      </c>
+      <c r="K2">
+        <v>15702687.604910919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
         <v>196</v>
@@ -1276,169 +1311,205 @@
       <c r="G3" t="s">
         <v>198</v>
       </c>
-      <c r="H3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J3">
-        <v>7967834.63756</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="H3">
+        <v>19028718.451565798</v>
+      </c>
+      <c r="I3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J3" t="s">
+        <v>273</v>
+      </c>
+      <c r="K3">
+        <v>19028718.451565798</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s">
         <v>196</v>
       </c>
       <c r="G4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J4">
-        <v>416736.8603415595</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>198</v>
+      </c>
+      <c r="H4">
+        <v>26104648.817951292</v>
+      </c>
+      <c r="I4" t="s">
+        <v>223</v>
+      </c>
+      <c r="K4">
+        <v>26104648.817951292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H5">
+        <v>6202897.0171400001</v>
+      </c>
+      <c r="I5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J5" t="s">
+        <v>269</v>
+      </c>
+      <c r="K5">
+        <v>6202897.0171400001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6">
+        <v>1600590.119251437</v>
+      </c>
+      <c r="I6" t="s">
+        <v>238</v>
+      </c>
+      <c r="J6" t="s">
+        <v>244</v>
+      </c>
+      <c r="K6">
+        <v>1600590.119251437</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H7">
+        <v>3063892.8050827952</v>
+      </c>
+      <c r="I7" t="s">
+        <v>228</v>
+      </c>
+      <c r="K7">
+        <v>3063892.8050827952</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" t="s">
+        <v>196</v>
+      </c>
+      <c r="G8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H8">
+        <v>110803.86577744479</v>
+      </c>
+      <c r="I8" t="s">
+        <v>228</v>
+      </c>
+      <c r="K8">
+        <v>110803.86577744479</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F9" t="s">
+        <v>196</v>
+      </c>
+      <c r="G9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9">
+        <v>21591249.4628</v>
+      </c>
+      <c r="I9" t="s">
+        <v>228</v>
+      </c>
+      <c r="K9">
+        <v>21591249.4628</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C10" t="s">
         <v>101</v>
-      </c>
-      <c r="E5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" t="s">
-        <v>198</v>
-      </c>
-      <c r="H5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I5" t="s">
-        <v>242</v>
-      </c>
-      <c r="J5">
-        <v>13233210.3886</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G6" t="s">
-        <v>198</v>
-      </c>
-      <c r="H6" t="s">
-        <v>214</v>
-      </c>
-      <c r="I6" t="s">
-        <v>243</v>
-      </c>
-      <c r="J6">
-        <v>22527998.6785</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G7" t="s">
-        <v>198</v>
-      </c>
-      <c r="H7" t="s">
-        <v>211</v>
-      </c>
-      <c r="I7" t="s">
-        <v>244</v>
-      </c>
-      <c r="J7">
-        <v>11531646.5435</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" t="s">
-        <v>196</v>
-      </c>
-      <c r="G8" t="s">
-        <v>200</v>
-      </c>
-      <c r="H8" t="s">
-        <v>211</v>
-      </c>
-      <c r="I8" t="s">
-        <v>245</v>
-      </c>
-      <c r="J8">
-        <v>4950459.91493</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" t="s">
-        <v>196</v>
-      </c>
-      <c r="G9" t="s">
-        <v>198</v>
-      </c>
-      <c r="H9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J9">
-        <v>63924259.8049</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>186</v>
@@ -1449,464 +1520,533 @@
       <c r="G10" t="s">
         <v>198</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10">
+        <v>13233210.388599999</v>
+      </c>
+      <c r="I10" t="s">
         <v>213</v>
       </c>
-      <c r="I10" t="s">
-        <v>246</v>
-      </c>
-      <c r="J10">
-        <v>12606786.4826</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="J10" t="s">
+        <v>242</v>
+      </c>
+      <c r="K10">
+        <v>13233210.388599999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E11" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F11" t="s">
         <v>196</v>
       </c>
       <c r="G11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H11" t="s">
-        <v>216</v>
-      </c>
-      <c r="J11">
-        <v>330003.3338055482</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>197</v>
+      </c>
+      <c r="H11">
+        <v>1929968.1763706871</v>
+      </c>
+      <c r="I11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K11">
+        <v>1929968.1763706871</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F12" t="s">
         <v>196</v>
       </c>
       <c r="G12" t="s">
-        <v>202</v>
-      </c>
-      <c r="H12" t="s">
-        <v>217</v>
-      </c>
-      <c r="J12">
-        <v>1058100.092748948</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>198</v>
+      </c>
+      <c r="H12">
+        <v>10276967.100669291</v>
+      </c>
+      <c r="I12" t="s">
+        <v>212</v>
+      </c>
+      <c r="J12" t="s">
+        <v>261</v>
+      </c>
+      <c r="K12">
+        <v>10276967.100669291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F13" t="s">
         <v>196</v>
       </c>
       <c r="G13" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13">
+        <v>9992991.5686563142</v>
+      </c>
+      <c r="I13" t="s">
+        <v>224</v>
+      </c>
+      <c r="K13">
+        <v>9992991.5686563142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F14" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" t="s">
+        <v>199</v>
+      </c>
+      <c r="H14">
+        <v>10340795.840703109</v>
+      </c>
+      <c r="I14" t="s">
+        <v>223</v>
+      </c>
+      <c r="K14">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15">
+        <v>352884.57374953461</v>
+      </c>
+      <c r="I15" t="s">
+        <v>212</v>
+      </c>
+      <c r="J15" t="s">
+        <v>261</v>
+      </c>
+      <c r="K15">
+        <v>352884.57374953461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G16" t="s">
+        <v>204</v>
+      </c>
+      <c r="H16">
+        <v>16826817.56129609</v>
+      </c>
+      <c r="I16" t="s">
+        <v>224</v>
+      </c>
+      <c r="J16" t="s">
+        <v>251</v>
+      </c>
+      <c r="K16">
+        <v>16826817.56129609</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F17" t="s">
+        <v>196</v>
+      </c>
+      <c r="G17" t="s">
+        <v>200</v>
+      </c>
+      <c r="H17">
+        <v>1445491.9253398541</v>
+      </c>
+      <c r="I17" t="s">
+        <v>212</v>
+      </c>
+      <c r="J17" t="s">
+        <v>244</v>
+      </c>
+      <c r="K17">
+        <v>1445491.9253398541</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G18" t="s">
+        <v>199</v>
+      </c>
+      <c r="H18">
+        <v>416736.86034155951</v>
+      </c>
+      <c r="I18" t="s">
+        <v>212</v>
+      </c>
+      <c r="K18">
+        <v>416736.86034155951</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F19" t="s">
+        <v>196</v>
+      </c>
+      <c r="G19" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19">
+        <v>3714363.081590083</v>
+      </c>
+      <c r="I19" t="s">
+        <v>223</v>
+      </c>
+      <c r="K19">
+        <v>3714363.081590083</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H20">
+        <v>7405086.2285420913</v>
+      </c>
+      <c r="I20" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" t="s">
+        <v>255</v>
+      </c>
+      <c r="K20">
+        <v>7405086.2285420913</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" t="s">
         <v>197</v>
       </c>
-      <c r="H13" t="s">
-        <v>218</v>
-      </c>
-      <c r="I13" t="s">
-        <v>247</v>
-      </c>
-      <c r="J13">
-        <v>363438.296974</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" t="s">
-        <v>187</v>
-      </c>
-      <c r="F14" t="s">
-        <v>196</v>
-      </c>
-      <c r="G14" t="s">
-        <v>201</v>
-      </c>
-      <c r="H14" t="s">
-        <v>219</v>
-      </c>
-      <c r="I14" t="s">
-        <v>248</v>
-      </c>
-      <c r="J14">
-        <v>2410689.221736038</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" t="s">
-        <v>187</v>
-      </c>
-      <c r="F15" t="s">
-        <v>196</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H21">
+        <v>1760913.595839669</v>
+      </c>
+      <c r="I21" t="s">
+        <v>226</v>
+      </c>
+      <c r="J21" t="s">
+        <v>254</v>
+      </c>
+      <c r="K21">
+        <v>1760913.595839669</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>190</v>
+      </c>
+      <c r="F22" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22" t="s">
+        <v>205</v>
+      </c>
+      <c r="H22">
+        <v>126962.74509226839</v>
+      </c>
+      <c r="I22" t="s">
+        <v>224</v>
+      </c>
+      <c r="J22" t="s">
+        <v>250</v>
+      </c>
+      <c r="K22">
+        <v>126962.74509226839</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" t="s">
+        <v>192</v>
+      </c>
+      <c r="F23" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" t="s">
+        <v>197</v>
+      </c>
+      <c r="H23">
+        <v>2161806.0909095029</v>
+      </c>
+      <c r="I23" t="s">
+        <v>228</v>
+      </c>
+      <c r="K23">
+        <v>2161806.0909095029</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" t="s">
+        <v>186</v>
+      </c>
+      <c r="F24" t="s">
+        <v>196</v>
+      </c>
+      <c r="G24" t="s">
+        <v>198</v>
+      </c>
+      <c r="H24">
+        <v>22527998.6785</v>
+      </c>
+      <c r="I24" t="s">
+        <v>214</v>
+      </c>
+      <c r="J24" t="s">
+        <v>243</v>
+      </c>
+      <c r="K24">
+        <v>22527998.6785</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" t="s">
+        <v>196</v>
+      </c>
+      <c r="G25" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25">
+        <v>1341835.17078</v>
+      </c>
+      <c r="I25" t="s">
+        <v>225</v>
+      </c>
+      <c r="J25" t="s">
+        <v>270</v>
+      </c>
+      <c r="K25">
+        <v>1341835.17078</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>192</v>
+      </c>
+      <c r="F26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" t="s">
         <v>203</v>
       </c>
-      <c r="H15" t="s">
-        <v>220</v>
-      </c>
-      <c r="J15">
-        <v>7481998.483051093</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F16" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" t="s">
-        <v>203</v>
-      </c>
-      <c r="H16" t="s">
-        <v>221</v>
-      </c>
-      <c r="I16" t="s">
-        <v>249</v>
-      </c>
-      <c r="J16">
-        <v>4789014.03756</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" t="s">
-        <v>188</v>
-      </c>
-      <c r="F17" t="s">
-        <v>196</v>
-      </c>
-      <c r="G17" t="s">
-        <v>201</v>
-      </c>
-      <c r="H17" t="s">
-        <v>222</v>
-      </c>
-      <c r="J17">
-        <v>163254.62437129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>188</v>
-      </c>
-      <c r="F18" t="s">
-        <v>196</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H26">
+        <v>3503071.0617284952</v>
+      </c>
+      <c r="I26" t="s">
+        <v>212</v>
+      </c>
+      <c r="J26" t="s">
+        <v>257</v>
+      </c>
+      <c r="K26">
+        <v>3503071.0617284952</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" t="s">
         <v>198</v>
       </c>
-      <c r="H18" t="s">
-        <v>223</v>
-      </c>
-      <c r="J18">
-        <v>10572188.5661376</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" t="s">
-        <v>188</v>
-      </c>
-      <c r="F19" t="s">
-        <v>196</v>
-      </c>
-      <c r="G19" t="s">
-        <v>197</v>
-      </c>
-      <c r="H19" t="s">
-        <v>213</v>
-      </c>
-      <c r="J19">
-        <v>1510729.369309124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F20" t="s">
-        <v>196</v>
-      </c>
-      <c r="G20" t="s">
-        <v>198</v>
-      </c>
-      <c r="H20" t="s">
-        <v>223</v>
-      </c>
-      <c r="J20">
-        <v>26104648.81795129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" t="s">
-        <v>188</v>
-      </c>
-      <c r="F21" t="s">
-        <v>196</v>
-      </c>
-      <c r="G21" t="s">
-        <v>199</v>
-      </c>
-      <c r="H21" t="s">
-        <v>223</v>
-      </c>
-      <c r="J21">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" t="s">
-        <v>188</v>
-      </c>
-      <c r="F22" t="s">
-        <v>196</v>
-      </c>
-      <c r="G22" t="s">
-        <v>198</v>
-      </c>
-      <c r="H22" t="s">
-        <v>212</v>
-      </c>
-      <c r="J22">
-        <v>4354811.166996506</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" t="s">
-        <v>189</v>
-      </c>
-      <c r="F23" t="s">
-        <v>196</v>
-      </c>
-      <c r="G23" t="s">
-        <v>198</v>
-      </c>
-      <c r="H23" t="s">
-        <v>212</v>
-      </c>
-      <c r="I23" t="s">
-        <v>250</v>
-      </c>
-      <c r="J23">
-        <v>3064668.693174671</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" t="s">
-        <v>190</v>
-      </c>
-      <c r="F24" t="s">
-        <v>196</v>
-      </c>
-      <c r="G24" t="s">
-        <v>204</v>
-      </c>
-      <c r="H24" t="s">
-        <v>224</v>
-      </c>
-      <c r="J24">
-        <v>9992991.568656314</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>190</v>
-      </c>
-      <c r="F25" t="s">
-        <v>196</v>
-      </c>
-      <c r="G25" t="s">
-        <v>204</v>
-      </c>
-      <c r="H25" t="s">
-        <v>224</v>
-      </c>
-      <c r="I25" t="s">
-        <v>251</v>
-      </c>
-      <c r="J25">
-        <v>16826817.56129609</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F26" t="s">
-        <v>196</v>
-      </c>
-      <c r="G26" t="s">
-        <v>205</v>
-      </c>
-      <c r="H26" t="s">
-        <v>224</v>
-      </c>
-      <c r="I26" t="s">
-        <v>250</v>
-      </c>
-      <c r="J26">
-        <v>126962.7450922684</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" t="s">
-        <v>177</v>
-      </c>
-      <c r="E27" t="s">
-        <v>191</v>
-      </c>
-      <c r="F27" t="s">
-        <v>196</v>
-      </c>
-      <c r="G27" t="s">
-        <v>201</v>
-      </c>
-      <c r="H27" t="s">
-        <v>212</v>
+      <c r="H27">
+        <v>63924259.804899998</v>
       </c>
       <c r="I27" t="s">
-        <v>252</v>
-      </c>
-      <c r="J27">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>215</v>
+      </c>
+      <c r="K27">
+        <v>63924259.804899998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>138</v>
+      </c>
+      <c r="D28" t="s">
+        <v>180</v>
       </c>
       <c r="E28" t="s">
         <v>192</v>
@@ -1915,24 +2055,30 @@
         <v>196</v>
       </c>
       <c r="G28" t="s">
-        <v>203</v>
-      </c>
-      <c r="H28" t="s">
-        <v>225</v>
+        <v>199</v>
+      </c>
+      <c r="H28">
+        <v>1141145.8646362079</v>
       </c>
       <c r="I28" t="s">
-        <v>250</v>
-      </c>
-      <c r="J28">
-        <v>22789723.43693621</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>212</v>
+      </c>
+      <c r="K28">
+        <v>1141145.8646362079</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>44</v>
+      </c>
+      <c r="B29" t="s">
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>132</v>
+      </c>
+      <c r="D29" t="s">
+        <v>180</v>
       </c>
       <c r="E29" t="s">
         <v>192</v>
@@ -1941,88 +2087,85 @@
         <v>196</v>
       </c>
       <c r="G29" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29">
+        <v>15428020.65126922</v>
+      </c>
+      <c r="I29" t="s">
+        <v>212</v>
+      </c>
+      <c r="J29" t="s">
+        <v>256</v>
+      </c>
+      <c r="K29">
+        <v>15428020.65126922</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" t="s">
         <v>200</v>
       </c>
-      <c r="H29" t="s">
-        <v>225</v>
-      </c>
-      <c r="I29" t="s">
-        <v>253</v>
-      </c>
-      <c r="J29">
-        <v>5804864.894492002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" t="s">
-        <v>178</v>
-      </c>
-      <c r="E30" t="s">
-        <v>192</v>
-      </c>
-      <c r="F30" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" t="s">
-        <v>197</v>
-      </c>
-      <c r="H30" t="s">
-        <v>226</v>
+      <c r="H30">
+        <v>5293594.021862885</v>
       </c>
       <c r="I30" t="s">
-        <v>254</v>
-      </c>
-      <c r="J30">
-        <v>1760913.595839669</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>239</v>
+      </c>
+      <c r="K30">
+        <v>5293594.021862885</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F31" t="s">
         <v>196</v>
       </c>
       <c r="G31" t="s">
-        <v>197</v>
-      </c>
-      <c r="H31" t="s">
-        <v>227</v>
+        <v>201</v>
+      </c>
+      <c r="H31">
+        <v>10235647.18904726</v>
       </c>
       <c r="I31" t="s">
-        <v>246</v>
-      </c>
-      <c r="J31">
-        <v>559241.2641449785</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>238</v>
+      </c>
+      <c r="K31">
+        <v>10235647.18904726</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
         <v>192</v>
@@ -2031,50 +2174,56 @@
         <v>196</v>
       </c>
       <c r="G32" t="s">
-        <v>201</v>
-      </c>
-      <c r="H32" t="s">
+        <v>200</v>
+      </c>
+      <c r="H32">
+        <v>4202253.5385999996</v>
+      </c>
+      <c r="I32" t="s">
+        <v>231</v>
+      </c>
+      <c r="J32" t="s">
+        <v>264</v>
+      </c>
+      <c r="K32">
+        <v>4202253.5385999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" t="s">
+        <v>198</v>
+      </c>
+      <c r="H33">
+        <v>3436361.1128654238</v>
+      </c>
+      <c r="I33" t="s">
         <v>212</v>
       </c>
-      <c r="J32">
-        <v>3512631.992361845</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E33" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" t="s">
-        <v>196</v>
-      </c>
-      <c r="G33" t="s">
-        <v>197</v>
-      </c>
-      <c r="H33" t="s">
-        <v>228</v>
-      </c>
-      <c r="J33">
-        <v>2161806.090909503</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="J33" t="s">
+        <v>267</v>
+      </c>
+      <c r="K33">
+        <v>3436361.1128654238</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
         <v>192</v>
@@ -2085,60 +2234,69 @@
       <c r="G34" t="s">
         <v>203</v>
       </c>
-      <c r="H34" t="s">
-        <v>212</v>
+      <c r="H34">
+        <v>8409093.1265900005</v>
       </c>
       <c r="I34" t="s">
-        <v>255</v>
-      </c>
-      <c r="J34">
-        <v>7405086.228542091</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>230</v>
+      </c>
+      <c r="J34" t="s">
+        <v>260</v>
+      </c>
+      <c r="K34">
+        <v>8409093.1265900005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="D35" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F35" t="s">
         <v>196</v>
       </c>
       <c r="G35" t="s">
-        <v>197</v>
-      </c>
-      <c r="H35" t="s">
-        <v>228</v>
-      </c>
-      <c r="J35">
-        <v>1929968.176370687</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>199</v>
+      </c>
+      <c r="H35">
+        <v>2331098.7137656999</v>
+      </c>
+      <c r="I35" t="s">
+        <v>237</v>
+      </c>
+      <c r="J35" t="s">
+        <v>274</v>
+      </c>
+      <c r="K35">
+        <v>2331098.7137656999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E36" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F36" t="s">
         <v>196</v>
@@ -2146,77 +2304,80 @@
       <c r="G36" t="s">
         <v>197</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36">
+        <v>363438.296974</v>
+      </c>
+      <c r="I36" t="s">
+        <v>218</v>
+      </c>
+      <c r="J36" t="s">
+        <v>247</v>
+      </c>
+      <c r="K36">
+        <v>363438.296974</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" t="s">
+        <v>200</v>
+      </c>
+      <c r="H37">
+        <v>11904079.93924279</v>
+      </c>
+      <c r="I37" t="s">
         <v>212</v>
       </c>
-      <c r="I36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J36">
-        <v>15428020.65126922</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" t="s">
-        <v>179</v>
-      </c>
-      <c r="E37" t="s">
-        <v>192</v>
-      </c>
-      <c r="F37" t="s">
-        <v>196</v>
-      </c>
-      <c r="G37" t="s">
-        <v>197</v>
-      </c>
-      <c r="H37" t="s">
-        <v>228</v>
-      </c>
-      <c r="J37">
-        <v>110803.8657774448</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="K37">
+        <v>11904079.93924279</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="E38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
         <v>196</v>
       </c>
       <c r="G38" t="s">
-        <v>203</v>
-      </c>
-      <c r="H38" t="s">
-        <v>212</v>
+        <v>200</v>
+      </c>
+      <c r="H38">
+        <v>5574423.9812850002</v>
       </c>
       <c r="I38" t="s">
-        <v>257</v>
-      </c>
-      <c r="J38">
-        <v>3503071.061728495</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>236</v>
+      </c>
+      <c r="J38" t="s">
+        <v>272</v>
+      </c>
+      <c r="K38">
+        <v>5574423.9812850002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
         <v>192</v>
@@ -2225,21 +2386,27 @@
         <v>196</v>
       </c>
       <c r="G39" t="s">
-        <v>197</v>
-      </c>
-      <c r="H39" t="s">
-        <v>229</v>
-      </c>
-      <c r="J39">
-        <v>989146.0724139999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="H39">
+        <v>5804864.8944920022</v>
+      </c>
+      <c r="I39" t="s">
+        <v>225</v>
+      </c>
+      <c r="J39" t="s">
+        <v>253</v>
+      </c>
+      <c r="K39">
+        <v>5804864.8944920022</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
         <v>192</v>
@@ -2248,79 +2415,82 @@
         <v>196</v>
       </c>
       <c r="G40" t="s">
-        <v>200</v>
-      </c>
-      <c r="H40" t="s">
-        <v>212</v>
+        <v>198</v>
+      </c>
+      <c r="H40">
+        <v>240468.70558949231</v>
       </c>
       <c r="I40" t="s">
-        <v>258</v>
-      </c>
-      <c r="J40">
-        <v>1874190.45757726</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>225</v>
+      </c>
+      <c r="K40">
+        <v>240468.70558949231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>84</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>172</v>
+      </c>
+      <c r="D41" t="s">
+        <v>185</v>
       </c>
       <c r="E41" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F41" t="s">
         <v>196</v>
       </c>
       <c r="G41" t="s">
-        <v>200</v>
-      </c>
-      <c r="H41" t="s">
-        <v>225</v>
+        <v>197</v>
+      </c>
+      <c r="H41">
+        <v>1973892.4554655049</v>
       </c>
       <c r="I41" t="s">
-        <v>259</v>
-      </c>
-      <c r="J41">
-        <v>6139378.49533</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>238</v>
+      </c>
+      <c r="K41">
+        <v>1973892.4554655049</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E42" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F42" t="s">
         <v>196</v>
       </c>
       <c r="G42" t="s">
-        <v>199</v>
-      </c>
-      <c r="H42" t="s">
-        <v>212</v>
-      </c>
-      <c r="J42">
-        <v>1141145.864636208</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>201</v>
+      </c>
+      <c r="H42">
+        <v>4412887.4395813216</v>
+      </c>
+      <c r="I42" t="s">
+        <v>238</v>
+      </c>
+      <c r="K42">
+        <v>4412887.4395813216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E43" t="s">
         <v>192</v>
@@ -2329,99 +2499,111 @@
         <v>196</v>
       </c>
       <c r="G43" t="s">
-        <v>198</v>
-      </c>
-      <c r="H43" t="s">
-        <v>225</v>
-      </c>
-      <c r="J43">
-        <v>240468.7055894923</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>197</v>
+      </c>
+      <c r="H43">
+        <v>989146.07241399994</v>
+      </c>
+      <c r="I43" t="s">
+        <v>229</v>
+      </c>
+      <c r="K43">
+        <v>989146.07241399994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>123</v>
+      </c>
+      <c r="D44" t="s">
+        <v>177</v>
       </c>
       <c r="E44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F44" t="s">
         <v>196</v>
       </c>
       <c r="G44" t="s">
+        <v>201</v>
+      </c>
+      <c r="H44">
+        <v>7644288.8516325541</v>
+      </c>
+      <c r="I44" t="s">
+        <v>212</v>
+      </c>
+      <c r="J44" t="s">
+        <v>252</v>
+      </c>
+      <c r="K44">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>115</v>
+      </c>
+      <c r="E45" t="s">
+        <v>188</v>
+      </c>
+      <c r="F45" t="s">
+        <v>196</v>
+      </c>
+      <c r="G45" t="s">
+        <v>197</v>
+      </c>
+      <c r="H45">
+        <v>1510729.3693091241</v>
+      </c>
+      <c r="I45" t="s">
+        <v>213</v>
+      </c>
+      <c r="K45">
+        <v>1510729.3693091241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>174</v>
+      </c>
+      <c r="E46" t="s">
+        <v>195</v>
+      </c>
+      <c r="F46" t="s">
+        <v>196</v>
+      </c>
+      <c r="G46" t="s">
         <v>203</v>
       </c>
-      <c r="H44" t="s">
-        <v>230</v>
-      </c>
-      <c r="I44" t="s">
-        <v>260</v>
-      </c>
-      <c r="J44">
-        <v>8409093.12659</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" t="s">
-        <v>192</v>
-      </c>
-      <c r="F45" t="s">
-        <v>196</v>
-      </c>
-      <c r="G45" t="s">
-        <v>198</v>
-      </c>
-      <c r="H45" t="s">
-        <v>212</v>
-      </c>
-      <c r="I45" t="s">
-        <v>261</v>
-      </c>
-      <c r="J45">
-        <v>10276967.10066929</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" t="s">
+      <c r="H46">
+        <v>3418676.16080696</v>
+      </c>
+      <c r="I46" t="s">
+        <v>213</v>
+      </c>
+      <c r="K46">
+        <v>3418676.16080696</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>54</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>142</v>
-      </c>
-      <c r="E46" t="s">
-        <v>192</v>
-      </c>
-      <c r="F46" t="s">
-        <v>196</v>
-      </c>
-      <c r="G46" t="s">
-        <v>199</v>
-      </c>
-      <c r="H46" t="s">
-        <v>212</v>
-      </c>
-      <c r="I46" t="s">
-        <v>262</v>
-      </c>
-      <c r="J46">
-        <v>948677.9026767507</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" t="s">
-        <v>143</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
@@ -2430,146 +2612,146 @@
         <v>196</v>
       </c>
       <c r="G47" t="s">
-        <v>200</v>
-      </c>
-      <c r="H47" t="s">
+        <v>199</v>
+      </c>
+      <c r="H47">
+        <v>948677.90267675067</v>
+      </c>
+      <c r="I47" t="s">
         <v>212</v>
       </c>
-      <c r="I47" t="s">
-        <v>261</v>
-      </c>
-      <c r="J47">
-        <v>352884.5737495346</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+      <c r="J47" t="s">
+        <v>262</v>
+      </c>
+      <c r="K47">
+        <v>948677.90267675067</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D48" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F48" t="s">
         <v>196</v>
       </c>
       <c r="G48" t="s">
-        <v>201</v>
-      </c>
-      <c r="H48" t="s">
-        <v>228</v>
-      </c>
-      <c r="J48">
-        <v>3063892.805082795</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>198</v>
+      </c>
+      <c r="H48">
+        <v>24972920.132110279</v>
+      </c>
+      <c r="I48" t="s">
+        <v>223</v>
+      </c>
+      <c r="J48" t="s">
+        <v>265</v>
+      </c>
+      <c r="K48">
+        <v>24972920.132110279</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="E49" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F49" t="s">
         <v>196</v>
       </c>
       <c r="G49" t="s">
-        <v>201</v>
-      </c>
-      <c r="H49" t="s">
-        <v>228</v>
+        <v>198</v>
+      </c>
+      <c r="H49">
+        <v>3064668.6931746709</v>
       </c>
       <c r="I49" t="s">
-        <v>254</v>
-      </c>
-      <c r="J49">
-        <v>1039802.195699128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>212</v>
+      </c>
+      <c r="J49" t="s">
+        <v>250</v>
+      </c>
+      <c r="K49">
+        <v>3064668.6931746709</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
-      </c>
-      <c r="D50" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="E50" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F50" t="s">
         <v>196</v>
       </c>
       <c r="G50" t="s">
-        <v>197</v>
-      </c>
-      <c r="H50" t="s">
-        <v>228</v>
-      </c>
-      <c r="J50">
-        <v>21591249.4628</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>198</v>
+      </c>
+      <c r="H50">
+        <v>12606786.4826</v>
+      </c>
+      <c r="I50" t="s">
+        <v>213</v>
+      </c>
+      <c r="J50" t="s">
+        <v>246</v>
+      </c>
+      <c r="K50">
+        <v>12606786.4826</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" t="s">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
-      </c>
-      <c r="D51" t="s">
-        <v>181</v>
+        <v>99</v>
       </c>
       <c r="E51" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F51" t="s">
         <v>196</v>
       </c>
       <c r="G51" t="s">
-        <v>197</v>
-      </c>
-      <c r="H51" t="s">
-        <v>212</v>
+        <v>198</v>
+      </c>
+      <c r="H51">
+        <v>7967834.6375599997</v>
       </c>
       <c r="I51" t="s">
-        <v>263</v>
-      </c>
-      <c r="J51">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>211</v>
+      </c>
+      <c r="K51">
+        <v>7967834.6375599997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E52" t="s">
         <v>192</v>
@@ -2580,31 +2762,28 @@
       <c r="G52" t="s">
         <v>200</v>
       </c>
-      <c r="H52" t="s">
-        <v>231</v>
+      <c r="H52">
+        <v>1550354.452950391</v>
       </c>
       <c r="I52" t="s">
-        <v>264</v>
-      </c>
-      <c r="J52">
-        <v>4202253.5386</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>225</v>
+      </c>
+      <c r="J52" t="s">
+        <v>251</v>
+      </c>
+      <c r="K52">
+        <v>1550354.452950391</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>149</v>
-      </c>
-      <c r="D53" t="s">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="E53" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s">
         <v>196</v>
@@ -2612,22 +2791,28 @@
       <c r="G53" t="s">
         <v>197</v>
       </c>
-      <c r="H53" t="s">
-        <v>232</v>
-      </c>
-      <c r="J53">
-        <v>1788407.819274</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="H53">
+        <v>1499689.8654100001</v>
+      </c>
+      <c r="I53" t="s">
+        <v>210</v>
+      </c>
+      <c r="J53" t="s">
+        <v>241</v>
+      </c>
+      <c r="K53">
+        <v>1499689.8654100001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="E54" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F54" t="s">
         <v>196</v>
@@ -2635,80 +2820,92 @@
       <c r="G54" t="s">
         <v>200</v>
       </c>
-      <c r="H54" t="s">
-        <v>225</v>
+      <c r="H54">
+        <v>4950459.91493</v>
       </c>
       <c r="I54" t="s">
-        <v>251</v>
-      </c>
-      <c r="J54">
-        <v>1550354.452950391</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>211</v>
+      </c>
+      <c r="J54" t="s">
+        <v>245</v>
+      </c>
+      <c r="K54">
+        <v>4950459.91493</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>22</v>
+      </c>
+      <c r="B55" t="s">
+        <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>110</v>
+      </c>
+      <c r="D55" t="s">
+        <v>175</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F55" t="s">
         <v>196</v>
       </c>
       <c r="G55" t="s">
-        <v>200</v>
-      </c>
-      <c r="H55" t="s">
-        <v>225</v>
+        <v>201</v>
+      </c>
+      <c r="H55">
+        <v>2410689.2217360381</v>
       </c>
       <c r="I55" t="s">
-        <v>246</v>
-      </c>
-      <c r="J55">
-        <v>7249147.17667</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>219</v>
+      </c>
+      <c r="J55" t="s">
+        <v>248</v>
+      </c>
+      <c r="K55">
+        <v>2410689.2217360381</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
         <v>196</v>
       </c>
       <c r="G56" t="s">
-        <v>198</v>
-      </c>
-      <c r="H56" t="s">
-        <v>223</v>
+        <v>197</v>
+      </c>
+      <c r="H56">
+        <v>1788407.8192739999</v>
       </c>
       <c r="I56" t="s">
-        <v>265</v>
-      </c>
-      <c r="J56">
-        <v>24972920.13211028</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <v>232</v>
+      </c>
+      <c r="K56">
+        <v>1788407.8192739999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E57" t="s">
         <v>193</v>
@@ -2717,21 +2914,27 @@
         <v>196</v>
       </c>
       <c r="G57" t="s">
-        <v>199</v>
-      </c>
-      <c r="H57" t="s">
-        <v>223</v>
-      </c>
-      <c r="J57">
-        <v>15702687.60491092</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="H57">
+        <v>2323252.9267690452</v>
+      </c>
+      <c r="I57" t="s">
+        <v>233</v>
+      </c>
+      <c r="J57" t="s">
+        <v>265</v>
+      </c>
+      <c r="K57">
+        <v>2323252.9267690452</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E58" t="s">
         <v>193</v>
@@ -2740,105 +2943,102 @@
         <v>196</v>
       </c>
       <c r="G58" t="s">
-        <v>203</v>
-      </c>
-      <c r="H58" t="s">
-        <v>224</v>
+        <v>206</v>
+      </c>
+      <c r="H58">
+        <v>2689687.0630099322</v>
       </c>
       <c r="I58" t="s">
-        <v>266</v>
-      </c>
-      <c r="J58">
-        <v>280723.3006520429</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>235</v>
+      </c>
+      <c r="K58">
+        <v>2689687.0630099322</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
-      </c>
-      <c r="D59" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F59" t="s">
         <v>196</v>
       </c>
       <c r="G59" t="s">
-        <v>199</v>
-      </c>
-      <c r="H59" t="s">
-        <v>223</v>
-      </c>
-      <c r="J59">
-        <v>3714363.081590083</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>201</v>
+      </c>
+      <c r="H59">
+        <v>163254.62437129</v>
+      </c>
+      <c r="I59" t="s">
+        <v>222</v>
+      </c>
+      <c r="K59">
+        <v>163254.62437129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F60" t="s">
         <v>196</v>
       </c>
       <c r="G60" t="s">
-        <v>200</v>
-      </c>
-      <c r="H60" t="s">
+        <v>198</v>
+      </c>
+      <c r="H60">
+        <v>4354811.166996506</v>
+      </c>
+      <c r="I60" t="s">
         <v>212</v>
       </c>
-      <c r="I60" t="s">
-        <v>244</v>
-      </c>
-      <c r="J60">
-        <v>1445491.925339854</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+      <c r="K60">
+        <v>4354811.166996506</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F61" t="s">
         <v>196</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
-      </c>
-      <c r="H61" t="s">
+        <v>201</v>
+      </c>
+      <c r="H61">
+        <v>3512631.992361845</v>
+      </c>
+      <c r="I61" t="s">
         <v>212</v>
       </c>
-      <c r="I61" t="s">
-        <v>267</v>
-      </c>
-      <c r="J61">
-        <v>3436361.112865424</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+      <c r="K61">
+        <v>3512631.992361845</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E62" t="s">
         <v>193</v>
@@ -2849,77 +3049,86 @@
       <c r="G62" t="s">
         <v>200</v>
       </c>
-      <c r="H62" t="s">
-        <v>233</v>
+      <c r="H62">
+        <v>2475749.7725005322</v>
       </c>
       <c r="I62" t="s">
-        <v>265</v>
-      </c>
-      <c r="J62">
-        <v>2323252.926769045</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>234</v>
+      </c>
+      <c r="J62" t="s">
+        <v>268</v>
+      </c>
+      <c r="K62">
+        <v>2475749.7725005322</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="C63" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="E63" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F63" t="s">
         <v>196</v>
       </c>
       <c r="G63" t="s">
-        <v>200</v>
-      </c>
-      <c r="H63" t="s">
-        <v>234</v>
+        <v>203</v>
+      </c>
+      <c r="H63">
+        <v>22789723.436936211</v>
       </c>
       <c r="I63" t="s">
-        <v>268</v>
-      </c>
-      <c r="J63">
-        <v>2475749.772500532</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>225</v>
+      </c>
+      <c r="J63" t="s">
+        <v>250</v>
+      </c>
+      <c r="K63">
+        <v>22789723.436936211</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="E64" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F64" t="s">
         <v>196</v>
       </c>
       <c r="G64" t="s">
-        <v>203</v>
-      </c>
-      <c r="H64" t="s">
-        <v>225</v>
+        <v>198</v>
+      </c>
+      <c r="H64">
+        <v>11531646.543500001</v>
       </c>
       <c r="I64" t="s">
-        <v>269</v>
-      </c>
-      <c r="J64">
-        <v>6202897.01714</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>211</v>
+      </c>
+      <c r="J64" t="s">
+        <v>244</v>
+      </c>
+      <c r="K64">
+        <v>11531646.543500001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C65" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F65" t="s">
         <v>196</v>
@@ -2927,22 +3136,25 @@
       <c r="G65" t="s">
         <v>200</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65">
+        <v>6139378.4953300003</v>
+      </c>
+      <c r="I65" t="s">
         <v>225</v>
       </c>
-      <c r="I65" t="s">
-        <v>270</v>
-      </c>
-      <c r="J65">
-        <v>1341835.17078</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+      <c r="J65" t="s">
+        <v>259</v>
+      </c>
+      <c r="K65">
+        <v>6139378.4953300003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C66" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E66" t="s">
         <v>193</v>
@@ -2951,73 +3163,85 @@
         <v>196</v>
       </c>
       <c r="G66" t="s">
+        <v>203</v>
+      </c>
+      <c r="H66">
+        <v>280723.3006520429</v>
+      </c>
+      <c r="I66" t="s">
+        <v>224</v>
+      </c>
+      <c r="J66" t="s">
+        <v>266</v>
+      </c>
+      <c r="K66">
+        <v>280723.3006520429</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F67" t="s">
+        <v>196</v>
+      </c>
+      <c r="G67" t="s">
+        <v>198</v>
+      </c>
+      <c r="H67">
+        <v>10572188.566137601</v>
+      </c>
+      <c r="I67" t="s">
+        <v>223</v>
+      </c>
+      <c r="K67">
+        <v>10572188.566137601</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" t="s">
+        <v>168</v>
+      </c>
+      <c r="D68" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" t="s">
+        <v>194</v>
+      </c>
+      <c r="F68" t="s">
+        <v>196</v>
+      </c>
+      <c r="G68" t="s">
         <v>201</v>
       </c>
-      <c r="H66" t="s">
-        <v>225</v>
-      </c>
-      <c r="I66" t="s">
-        <v>271</v>
-      </c>
-      <c r="J66">
-        <v>1113516.59973</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" t="s">
-        <v>163</v>
-      </c>
-      <c r="E67" t="s">
-        <v>193</v>
-      </c>
-      <c r="F67" t="s">
-        <v>196</v>
-      </c>
-      <c r="G67" t="s">
-        <v>206</v>
-      </c>
-      <c r="H67" t="s">
-        <v>235</v>
-      </c>
-      <c r="J67">
-        <v>2689687.063009932</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>76</v>
-      </c>
-      <c r="C68" t="s">
-        <v>164</v>
-      </c>
-      <c r="E68" t="s">
-        <v>193</v>
-      </c>
-      <c r="F68" t="s">
-        <v>196</v>
-      </c>
-      <c r="G68" t="s">
-        <v>200</v>
-      </c>
-      <c r="H68" t="s">
-        <v>236</v>
+      <c r="H68">
+        <v>517003.99124031531</v>
       </c>
       <c r="I68" t="s">
-        <v>272</v>
-      </c>
-      <c r="J68">
-        <v>5574423.981285</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>212</v>
+      </c>
+      <c r="K68">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E69" t="s">
         <v>193</v>
@@ -3026,134 +3250,155 @@
         <v>196</v>
       </c>
       <c r="G69" t="s">
-        <v>198</v>
-      </c>
-      <c r="H69" t="s">
+        <v>201</v>
+      </c>
+      <c r="H69">
+        <v>1113516.5997299999</v>
+      </c>
+      <c r="I69" t="s">
         <v>225</v>
       </c>
-      <c r="I69" t="s">
-        <v>273</v>
-      </c>
-      <c r="J69">
-        <v>19028718.4515658</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+      <c r="J69" t="s">
+        <v>271</v>
+      </c>
+      <c r="K69">
+        <v>1113516.5997299999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
-        <v>166</v>
+        <v>107</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E70" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F70" t="s">
         <v>196</v>
       </c>
       <c r="G70" t="s">
-        <v>199</v>
-      </c>
-      <c r="H70" t="s">
-        <v>237</v>
+        <v>201</v>
+      </c>
+      <c r="H70">
+        <v>330003.3338055482</v>
       </c>
       <c r="I70" t="s">
-        <v>274</v>
-      </c>
-      <c r="J70">
-        <v>2331098.7137657</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>216</v>
+      </c>
+      <c r="K70">
+        <v>330003.3338055482</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>57</v>
+      </c>
+      <c r="B71" t="s">
+        <v>90</v>
       </c>
       <c r="C71" t="s">
-        <v>167</v>
+        <v>145</v>
+      </c>
+      <c r="D71" t="s">
+        <v>178</v>
       </c>
       <c r="E71" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F71" t="s">
         <v>196</v>
       </c>
       <c r="G71" t="s">
-        <v>200</v>
-      </c>
-      <c r="H71" t="s">
-        <v>212</v>
-      </c>
-      <c r="J71">
-        <v>11904079.93924279</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>201</v>
+      </c>
+      <c r="H71">
+        <v>1039802.195699128</v>
+      </c>
+      <c r="I71" t="s">
+        <v>228</v>
+      </c>
+      <c r="J71" t="s">
+        <v>254</v>
+      </c>
+      <c r="K71">
+        <v>1039802.195699128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>168</v>
-      </c>
-      <c r="D72" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F72" t="s">
         <v>196</v>
       </c>
       <c r="G72" t="s">
-        <v>201</v>
-      </c>
-      <c r="H72" t="s">
-        <v>212</v>
-      </c>
-      <c r="J72">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>202</v>
+      </c>
+      <c r="H72">
+        <v>1058100.0927489479</v>
+      </c>
+      <c r="I72" t="s">
+        <v>217</v>
+      </c>
+      <c r="K72">
+        <v>1058100.0927489479</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="C73" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F73" t="s">
         <v>196</v>
       </c>
       <c r="G73" t="s">
-        <v>201</v>
-      </c>
-      <c r="H73" t="s">
-        <v>238</v>
-      </c>
-      <c r="J73">
-        <v>4412887.439581322</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+        <v>203</v>
+      </c>
+      <c r="H73">
+        <v>7481998.4830510933</v>
+      </c>
+      <c r="I73" t="s">
+        <v>220</v>
+      </c>
+      <c r="K73">
+        <v>7481998.4830510933</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>59</v>
+      </c>
+      <c r="B74" t="s">
+        <v>93</v>
       </c>
       <c r="C74" t="s">
-        <v>170</v>
+        <v>147</v>
+      </c>
+      <c r="D74" t="s">
+        <v>181</v>
       </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F74" t="s">
         <v>196</v>
@@ -3161,83 +3406,92 @@
       <c r="G74" t="s">
         <v>197</v>
       </c>
-      <c r="H74" t="s">
-        <v>238</v>
+      <c r="H74">
+        <v>1464485.5013698239</v>
       </c>
       <c r="I74" t="s">
-        <v>244</v>
-      </c>
-      <c r="J74">
-        <v>1600590.119251437</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>212</v>
+      </c>
+      <c r="J74" t="s">
+        <v>263</v>
+      </c>
+      <c r="K74">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C75" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E75" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F75" t="s">
         <v>196</v>
       </c>
       <c r="G75" t="s">
-        <v>201</v>
-      </c>
-      <c r="H75" t="s">
-        <v>238</v>
-      </c>
-      <c r="J75">
-        <v>10235647.18904726</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>197</v>
+      </c>
+      <c r="H75">
+        <v>559241.26414497849</v>
+      </c>
+      <c r="I75" t="s">
+        <v>227</v>
+      </c>
+      <c r="J75" t="s">
+        <v>246</v>
+      </c>
+      <c r="K75">
+        <v>559241.26414497849</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
-      </c>
-      <c r="D76" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="E76" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F76" t="s">
         <v>196</v>
       </c>
       <c r="G76" t="s">
-        <v>197</v>
-      </c>
-      <c r="H76" t="s">
-        <v>238</v>
-      </c>
-      <c r="J76">
-        <v>1973892.455465505</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>203</v>
+      </c>
+      <c r="H76">
+        <v>4789014.0375600001</v>
+      </c>
+      <c r="I76" t="s">
+        <v>221</v>
+      </c>
+      <c r="J76" t="s">
+        <v>249</v>
+      </c>
+      <c r="K76">
+        <v>4789014.0375600001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="E77" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F77" t="s">
         <v>196</v>
@@ -3245,37 +3499,49 @@
       <c r="G77" t="s">
         <v>200</v>
       </c>
-      <c r="H77" t="s">
-        <v>239</v>
-      </c>
-      <c r="J77">
-        <v>5293594.021862885</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+      <c r="H77">
+        <v>7249147.17667</v>
+      </c>
+      <c r="I77" t="s">
+        <v>225</v>
+      </c>
+      <c r="J77" t="s">
+        <v>246</v>
+      </c>
+      <c r="K77">
+        <v>7249147.17667</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="E78" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F78" t="s">
         <v>196</v>
       </c>
       <c r="G78" t="s">
-        <v>203</v>
-      </c>
-      <c r="H78" t="s">
-        <v>213</v>
-      </c>
-      <c r="J78">
-        <v>3418676.16080696</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="H78">
+        <v>1874190.45757726</v>
+      </c>
+      <c r="I78" t="s">
+        <v>212</v>
+      </c>
+      <c r="J78" t="s">
+        <v>258</v>
+      </c>
+      <c r="K78">
+        <v>1874190.45757726</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>89</v>
       </c>
@@ -3288,17 +3554,20 @@
       <c r="G79" t="s">
         <v>201</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79">
+        <v>7644288.8516325541</v>
+      </c>
+      <c r="I79" t="s">
         <v>212</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>252</v>
       </c>
-      <c r="J79">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+      <c r="K79">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>92</v>
       </c>
@@ -3311,17 +3580,20 @@
       <c r="G80" t="s">
         <v>207</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80">
+        <v>16569166.515905419</v>
+      </c>
+      <c r="I80" t="s">
         <v>212</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>256</v>
       </c>
-      <c r="J80">
-        <v>16569166.51590542</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10">
+      <c r="K80">
+        <v>16569166.515905419</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>94</v>
       </c>
@@ -3334,17 +3606,20 @@
       <c r="G81" t="s">
         <v>198</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81">
+        <v>28687283.213700362</v>
+      </c>
+      <c r="I81" t="s">
         <v>223</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>265</v>
       </c>
-      <c r="J81">
-        <v>28687283.21370036</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10">
+      <c r="K81">
+        <v>28687283.213700362</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>93</v>
       </c>
@@ -3357,17 +3632,20 @@
       <c r="G82" t="s">
         <v>197</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82">
+        <v>1464485.5013698239</v>
+      </c>
+      <c r="I82" t="s">
         <v>212</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>263</v>
       </c>
-      <c r="J82">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10">
+      <c r="K82">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>96</v>
       </c>
@@ -3380,14 +3658,17 @@
       <c r="G83" t="s">
         <v>201</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83">
+        <v>517003.99124031531</v>
+      </c>
+      <c r="I83" t="s">
         <v>212</v>
       </c>
-      <c r="J83">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10">
+      <c r="K83">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>97</v>
       </c>
@@ -3400,14 +3681,17 @@
       <c r="G84" t="s">
         <v>208</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84">
+        <v>12209539.644512771</v>
+      </c>
+      <c r="I84" t="s">
         <v>238</v>
       </c>
-      <c r="J84">
-        <v>12209539.64451277</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10">
+      <c r="K84">
+        <v>12209539.644512771</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>95</v>
       </c>
@@ -3420,17 +3704,20 @@
       <c r="G85" t="s">
         <v>199</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85">
+        <v>2331098.7137656999</v>
+      </c>
+      <c r="I85" t="s">
         <v>237</v>
       </c>
-      <c r="I85" t="s">
+      <c r="J85" t="s">
         <v>274</v>
       </c>
-      <c r="J85">
-        <v>2331098.7137657</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10">
+      <c r="K85">
+        <v>2331098.7137656999</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>88</v>
       </c>
@@ -3443,14 +3730,17 @@
       <c r="G86" t="s">
         <v>199</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86">
+        <v>10340795.840703109</v>
+      </c>
+      <c r="I86" t="s">
         <v>223</v>
       </c>
-      <c r="J86">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10">
+      <c r="K86">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>87</v>
       </c>
@@ -3463,17 +3753,20 @@
       <c r="G87" t="s">
         <v>208</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87">
+        <v>3104130.8525155862</v>
+      </c>
+      <c r="I87" t="s">
         <v>218</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>275</v>
       </c>
-      <c r="J87">
-        <v>3104130.852515586</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10">
+      <c r="K87">
+        <v>3104130.8525155862</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>91</v>
       </c>
@@ -3486,17 +3779,20 @@
       <c r="G88" t="s">
         <v>209</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88">
+        <v>29416961.665085409</v>
+      </c>
+      <c r="I88" t="s">
         <v>228</v>
       </c>
-      <c r="I88" t="s">
+      <c r="J88" t="s">
         <v>246</v>
       </c>
-      <c r="J88">
-        <v>29416961.66508541</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10">
+      <c r="K88">
+        <v>29416961.665085409</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>90</v>
       </c>
@@ -3509,17 +3805,25 @@
       <c r="G89" t="s">
         <v>209</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89">
+        <v>4589123.6108127972</v>
+      </c>
+      <c r="I89" t="s">
         <v>240</v>
       </c>
-      <c r="I89" t="s">
+      <c r="J89" t="s">
         <v>254</v>
       </c>
-      <c r="J89">
-        <v>4589123.610812797</v>
+      <c r="K89">
+        <v>4589123.6108127972</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K89">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>